--- a/research/traditional_assets/database/data/taiwan/taiwan_broadcasting.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_broadcasting.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tpex_8487" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.024</v>
+        <v>0.0246</v>
       </c>
       <c r="G2">
-        <v>-0.008091334894613583</v>
+        <v>0.05082177161152615</v>
       </c>
       <c r="H2">
-        <v>-0.008091334894613583</v>
+        <v>0.05082177161152615</v>
       </c>
       <c r="I2">
-        <v>-0.07069086651053864</v>
+        <v>-0.007161152614727855</v>
       </c>
       <c r="J2">
-        <v>-0.07069086651053864</v>
+        <v>-0.005678379149513198</v>
       </c>
       <c r="K2">
-        <v>-2.785</v>
+        <v>2.878</v>
       </c>
       <c r="L2">
-        <v>-0.0326112412177986</v>
+        <v>0.03071504802561366</v>
       </c>
       <c r="M2">
-        <v>0.367</v>
+        <v>0.716</v>
       </c>
       <c r="N2">
-        <v>0.002736763609246831</v>
+        <v>0.00599163179916318</v>
       </c>
       <c r="O2">
-        <v>-0.1317773788150808</v>
+        <v>0.2487838776928422</v>
       </c>
       <c r="P2">
-        <v>0.367</v>
+        <v>0.716</v>
       </c>
       <c r="Q2">
-        <v>0.002736763609246831</v>
+        <v>0.00599163179916318</v>
       </c>
       <c r="R2">
-        <v>-0.1317773788150808</v>
+        <v>0.2487838776928422</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.8</v>
+        <v>26.29</v>
       </c>
       <c r="V2">
-        <v>0.1998508575689784</v>
+        <v>0.22</v>
       </c>
       <c r="W2">
-        <v>-0.02669039145907473</v>
+        <v>0.01410714285714286</v>
       </c>
       <c r="X2">
-        <v>0.06072813889281154</v>
+        <v>0.09454719890614592</v>
       </c>
       <c r="Y2">
-        <v>-0.08741853035188628</v>
+        <v>-0.08044005604900306</v>
       </c>
       <c r="Z2">
-        <v>0.4246432300730943</v>
+        <v>0.4581235026646459</v>
       </c>
       <c r="AA2">
-        <v>-0.04279374471682164</v>
+        <v>-0.0009212305345532363</v>
       </c>
       <c r="AB2">
-        <v>0.05252087757475747</v>
+        <v>0.09094335941831919</v>
       </c>
       <c r="AC2">
-        <v>-0.09542145952590865</v>
+        <v>-0.09139664738518857</v>
       </c>
       <c r="AD2">
-        <v>97.36999999999999</v>
+        <v>82.17999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>97.36999999999999</v>
+        <v>82.17999999999999</v>
       </c>
       <c r="AG2">
-        <v>70.56999999999999</v>
+        <v>55.88999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.4206592646995291</v>
+        <v>0.4074771915906386</v>
       </c>
       <c r="AI2">
-        <v>0.420913846020836</v>
+        <v>0.3898297044732223</v>
       </c>
       <c r="AJ2">
-        <v>0.3447989446425954</v>
+        <v>0.3186612691715605</v>
       </c>
       <c r="AK2">
-        <v>0.3450349581968415</v>
+        <v>0.3028939952308693</v>
       </c>
       <c r="AL2">
-        <v>1.107</v>
+        <v>1.077</v>
       </c>
       <c r="AM2">
-        <v>0.988</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="AN2">
-        <v>-450.7870370370366</v>
+        <v>26.70783230419239</v>
       </c>
       <c r="AO2">
-        <v>-5.453477868112015</v>
+        <v>-0.6230269266480967</v>
       </c>
       <c r="AP2">
-        <v>-326.7129629629626</v>
+        <v>18.16379590510237</v>
       </c>
       <c r="AQ2">
-        <v>-6.110323886639677</v>
+        <v>-0.7373626373626375</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Television Enterprise Co.,Ltd. (TPEX:8329)</t>
+          <t>ELTA Technology Co.,Ltd. (TPEX:8487)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,115 +721,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.024</v>
+        <v>0.0479</v>
       </c>
       <c r="G3">
-        <v>0.005978835978835979</v>
+        <v>0.071484375</v>
       </c>
       <c r="H3">
-        <v>0.005978835978835979</v>
+        <v>0.071484375</v>
       </c>
       <c r="I3">
-        <v>-0.03227513227513228</v>
+        <v>0.0578125</v>
       </c>
       <c r="J3">
-        <v>-0.03227513227513228</v>
+        <v>0.04771511130136986</v>
       </c>
       <c r="K3">
-        <v>-1.04</v>
+        <v>1.2</v>
       </c>
       <c r="L3">
-        <v>-0.02751322751322752</v>
+        <v>0.04687499999999999</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.716</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03377358490566038</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.5966666666666667</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.716</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03377358490566038</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.5966666666666667</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>12.4</v>
+        <v>4.84</v>
       </c>
       <c r="V3">
-        <v>0.1551939924906132</v>
+        <v>0.2283018867924528</v>
       </c>
       <c r="W3">
-        <v>-0.009710550887021475</v>
+        <v>0.1435406698564593</v>
       </c>
       <c r="X3">
-        <v>0.05456212360889379</v>
+        <v>0.09454719890614592</v>
       </c>
       <c r="Y3">
-        <v>-0.06427267449591526</v>
+        <v>0.04899347095031341</v>
       </c>
       <c r="Z3">
-        <v>0.3802816901408451</v>
+        <v>5.953488372093022</v>
       </c>
       <c r="AA3">
-        <v>-0.01227364185110664</v>
+        <v>0.2840713603058299</v>
       </c>
       <c r="AB3">
-        <v>0.05248817413191342</v>
+        <v>0.09094335941831919</v>
       </c>
       <c r="AC3">
-        <v>-0.06476181598302007</v>
+        <v>0.1931280008875107</v>
       </c>
       <c r="AD3">
-        <v>5.58</v>
+        <v>1.86</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.58</v>
+        <v>1.86</v>
       </c>
       <c r="AG3">
-        <v>-6.82</v>
+        <v>-2.98</v>
       </c>
       <c r="AH3">
-        <v>0.06527842770238652</v>
+        <v>0.08065915004336514</v>
       </c>
       <c r="AI3">
-        <v>0.04745705051879572</v>
+        <v>0.1739943872778298</v>
       </c>
       <c r="AJ3">
-        <v>-0.09332238642583469</v>
+        <v>-0.1635565312843029</v>
       </c>
       <c r="AK3">
-        <v>-0.06484122456740825</v>
+        <v>-0.5094017094017093</v>
       </c>
       <c r="AL3">
-        <v>0.049</v>
+        <v>0.064</v>
       </c>
       <c r="AM3">
-        <v>0.021</v>
+        <v>0.059</v>
       </c>
       <c r="AN3">
-        <v>3.902097902097903</v>
+        <v>1.127272727272727</v>
       </c>
       <c r="AO3">
-        <v>-24.89795918367347</v>
+        <v>23.125</v>
       </c>
       <c r="AP3">
-        <v>-4.76923076923077</v>
+        <v>-1.806060606060606</v>
       </c>
       <c r="AQ3">
-        <v>-58.09523809523809</v>
+        <v>25.08474576271186</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +843,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>China Television Company, Ltd. (TWSE:9928)</t>
+          <t>Taiwan Television Enterprise Co.,Ltd. (TPEX:8329)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,25 +852,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0257</v>
+        <v>0.00792</v>
       </c>
       <c r="G4">
-        <v>-0.007992831541218638</v>
+        <v>0.09318734793187347</v>
       </c>
       <c r="H4">
-        <v>-0.007992831541218638</v>
+        <v>0.09318734793187347</v>
       </c>
       <c r="I4">
-        <v>-0.1451612903225807</v>
+        <v>-0.002700729927007299</v>
       </c>
       <c r="J4">
-        <v>-0.1451612903225807</v>
+        <v>-0.002357543251199742</v>
       </c>
       <c r="K4">
-        <v>-1.52</v>
+        <v>1.58</v>
       </c>
       <c r="L4">
-        <v>-0.05448028673835126</v>
+        <v>0.03844282238442823</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,7 +879,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -883,79 +888,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.15</v>
+        <v>16.7</v>
       </c>
       <c r="V4">
-        <v>0.1454802259887006</v>
+        <v>0.2609375</v>
       </c>
       <c r="W4">
-        <v>-0.1078014184397163</v>
+        <v>0.01410714285714286</v>
       </c>
       <c r="X4">
-        <v>0.1256173647716172</v>
+        <v>0.09428993816366207</v>
       </c>
       <c r="Y4">
-        <v>-0.2334187832113335</v>
+        <v>-0.08018279530651921</v>
       </c>
       <c r="Z4">
-        <v>0.2948013524936602</v>
+        <v>0.3907586993725043</v>
       </c>
       <c r="AA4">
-        <v>-0.04279374471682164</v>
+        <v>-0.0009212305345532363</v>
       </c>
       <c r="AB4">
-        <v>0.05262771480908701</v>
+        <v>0.09047541685063534</v>
       </c>
       <c r="AC4">
-        <v>-0.09542145952590865</v>
+        <v>-0.09139664738518857</v>
       </c>
       <c r="AD4">
-        <v>86.59999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>86.59999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="AG4">
-        <v>81.44999999999999</v>
+        <v>-11.48</v>
       </c>
       <c r="AH4">
-        <v>0.7098360655737704</v>
+        <v>0.07541173071366657</v>
       </c>
       <c r="AI4">
-        <v>0.8642714570858284</v>
+        <v>0.04668216776962976</v>
       </c>
       <c r="AJ4">
-        <v>0.6970474967907573</v>
+        <v>-0.2185833968012186</v>
       </c>
       <c r="AK4">
-        <v>0.8569174118884798</v>
+        <v>-0.1206896551724138</v>
       </c>
       <c r="AL4">
-        <v>0.979</v>
+        <v>0.049</v>
       </c>
       <c r="AM4">
-        <v>0.895</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="AN4">
-        <v>-79.44954128440367</v>
+        <v>2.868131868131868</v>
       </c>
       <c r="AO4">
-        <v>-4.136874361593462</v>
+        <v>-2.26530612244898</v>
       </c>
       <c r="AP4">
-        <v>-74.72477064220182</v>
+        <v>-6.307692307692307</v>
       </c>
       <c r="AQ4">
-        <v>-4.525139664804469</v>
+        <v>-36.99999999999996</v>
       </c>
     </row>
     <row r="5">
@@ -966,127 +971,8836 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>China Television Company, Ltd. (TWSE:9928)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Broadcasting</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0246</v>
+      </c>
+      <c r="G5">
+        <v>-0.03325925925925926</v>
+      </c>
+      <c r="H5">
+        <v>-0.03325925925925926</v>
+      </c>
+      <c r="I5">
+        <v>-0.07555555555555556</v>
+      </c>
+      <c r="J5">
+        <v>-0.05141975308641976</v>
+      </c>
+      <c r="K5">
+        <v>0.098</v>
+      </c>
+      <c r="L5">
+        <v>0.00362962962962963</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>4.75</v>
+      </c>
+      <c r="V5">
+        <v>0.1384839650145773</v>
+      </c>
+      <c r="W5">
+        <v>0.007205882352941177</v>
+      </c>
+      <c r="X5">
+        <v>0.1821337789110791</v>
+      </c>
+      <c r="Y5">
+        <v>-0.1749278965581379</v>
+      </c>
+      <c r="Z5">
+        <v>0.2840610205155182</v>
+      </c>
+      <c r="AA5">
+        <v>-0.01460634753638436</v>
+      </c>
+      <c r="AB5">
+        <v>0.09133661617285707</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1059429637092414</v>
+      </c>
+      <c r="AD5">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AG5">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.6864716636197441</v>
+      </c>
+      <c r="AI5">
+        <v>0.8505096262740657</v>
+      </c>
+      <c r="AJ5">
+        <v>0.6722408026755853</v>
+      </c>
+      <c r="AK5">
+        <v>0.8420107719928186</v>
+      </c>
+      <c r="AL5">
+        <v>0.964</v>
+      </c>
+      <c r="AM5">
+        <v>0.848</v>
+      </c>
+      <c r="AN5">
+        <v>-191.0941475826972</v>
+      </c>
+      <c r="AO5">
+        <v>-2.116182572614108</v>
+      </c>
+      <c r="AP5">
+        <v>-179.0076335877862</v>
+      </c>
+      <c r="AQ5">
+        <v>-2.405660377358491</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>ELTA Technology Co.,Ltd. (TPEX:8487)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TPEX:8487</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Broadcasting</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0806591500433651</v>
+      </c>
+      <c r="F2">
+        <v>0.13</v>
+      </c>
+      <c r="G2">
+        <v>21.2</v>
+      </c>
+      <c r="H2">
+        <v>20.5780106492148</v>
+      </c>
+      <c r="I2">
+        <v>18.22</v>
+      </c>
+      <c r="J2">
+        <v>18.7358106492148</v>
+      </c>
+      <c r="K2">
+        <v>1.86</v>
+      </c>
+      <c r="L2">
+        <v>2.9978</v>
+      </c>
+      <c r="M2">
+        <v>0.0909433594183192</v>
+      </c>
+      <c r="N2">
+        <v>0.0894118343782275</v>
+      </c>
+      <c r="O2">
+        <v>0.0498673394495413</v>
+      </c>
+      <c r="P2">
+        <v>0.03784</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.09454719890614589</v>
+      </c>
+      <c r="T2">
+        <v>0.09711797054968679</v>
+      </c>
+      <c r="U2">
+        <v>0.802254528502544</v>
+      </c>
+      <c r="V2">
+        <v>0.839250345929152</v>
+      </c>
+      <c r="W2">
+        <v>10.43753438920748</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>21.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.65</v>
+      </c>
+      <c r="AH2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.375</v>
+      </c>
+      <c r="AJ2">
+        <v>1.86</v>
+      </c>
+      <c r="AK2">
+        <v>1.86</v>
+      </c>
+      <c r="AL2">
+        <v>0.064</v>
+      </c>
+      <c r="AM2">
+        <v>1.86</v>
+      </c>
+      <c r="AN2">
+        <v>4.84</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09089100038832393</v>
+      </c>
+      <c r="C2">
+        <v>23.07716495353753</v>
+      </c>
+      <c r="D2">
+        <v>18.23716495353753</v>
+      </c>
+      <c r="E2">
+        <v>-1.86</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.84</v>
+      </c>
+      <c r="H2">
+        <v>21.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.65</v>
+      </c>
+      <c r="K2">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L2">
+        <v>1.48</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.48</v>
+      </c>
+      <c r="O2">
+        <v>0.2959999999999999</v>
+      </c>
+      <c r="P2">
+        <v>1.184</v>
+      </c>
+      <c r="Q2">
+        <v>1.354</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09089100038832393</v>
+      </c>
+      <c r="T2">
+        <v>0.7496383993412342</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09076441838754727</v>
+      </c>
+      <c r="C3">
+        <v>22.88819646900912</v>
+      </c>
+      <c r="D3">
+        <v>18.27879646900912</v>
+      </c>
+      <c r="E3">
+        <v>-1.6294</v>
+      </c>
+      <c r="F3">
+        <v>0.2306</v>
+      </c>
+      <c r="G3">
+        <v>4.84</v>
+      </c>
+      <c r="H3">
+        <v>21.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.65</v>
+      </c>
+      <c r="K3">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L3">
+        <v>1.48</v>
+      </c>
+      <c r="M3">
+        <v>0.01053842</v>
+      </c>
+      <c r="N3">
+        <v>1.46946158</v>
+      </c>
+      <c r="O3">
+        <v>0.2938923159999999</v>
+      </c>
+      <c r="P3">
+        <v>1.175569264</v>
+      </c>
+      <c r="Q3">
+        <v>1.345569264</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09131193776519927</v>
+      </c>
+      <c r="T3">
+        <v>0.7556960833763149</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>140.4385097576297</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09063783638677064</v>
+      </c>
+      <c r="C4">
+        <v>22.69941849091309</v>
+      </c>
+      <c r="D4">
+        <v>18.32061849091309</v>
+      </c>
+      <c r="E4">
+        <v>-1.3988</v>
+      </c>
+      <c r="F4">
+        <v>0.4612</v>
+      </c>
+      <c r="G4">
+        <v>4.84</v>
+      </c>
+      <c r="H4">
+        <v>21.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.65</v>
+      </c>
+      <c r="K4">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L4">
+        <v>1.48</v>
+      </c>
+      <c r="M4">
+        <v>0.02107684</v>
+      </c>
+      <c r="N4">
+        <v>1.45892316</v>
+      </c>
+      <c r="O4">
+        <v>0.2917846319999999</v>
+      </c>
+      <c r="P4">
+        <v>1.167138528</v>
+      </c>
+      <c r="Q4">
+        <v>1.337138528</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09174146570078637</v>
+      </c>
+      <c r="T4">
+        <v>0.7618773936161931</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>70.21925487881484</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09051125438599397</v>
+      </c>
+      <c r="C5">
+        <v>22.51083232988863</v>
+      </c>
       <c r="D5">
-        <v>-0.0042</v>
+        <v>18.36263232988863</v>
+      </c>
+      <c r="E5">
+        <v>-1.1682</v>
+      </c>
+      <c r="F5">
+        <v>0.6918</v>
       </c>
       <c r="G5">
-        <v>-0.03522842639593909</v>
+        <v>4.84</v>
       </c>
       <c r="H5">
-        <v>-0.03522842639593909</v>
+        <v>21.2</v>
       </c>
       <c r="I5">
-        <v>-0.03893401015228427</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-0.03893401015228427</v>
+        <v>1.65</v>
       </c>
       <c r="K5">
-        <v>-0.225</v>
+        <v>0.1699999999999999</v>
       </c>
       <c r="L5">
-        <v>-0.01142131979695432</v>
+        <v>1.48</v>
       </c>
       <c r="M5">
-        <v>0.367</v>
+        <v>0.03161526</v>
       </c>
       <c r="N5">
-        <v>0.01952127659574468</v>
+        <v>1.44838474</v>
       </c>
       <c r="O5">
-        <v>-1.631111111111111</v>
+        <v>0.2896769479999999</v>
       </c>
       <c r="P5">
-        <v>0.367</v>
+        <v>1.158707792</v>
       </c>
       <c r="Q5">
-        <v>0.01952127659574468</v>
+        <v>1.328707792</v>
       </c>
       <c r="R5">
-        <v>-1.631111111111111</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.09217984988246802</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.7681861535517389</v>
       </c>
       <c r="U5">
-        <v>9.25</v>
+        <v>0.0457</v>
       </c>
       <c r="V5">
-        <v>0.4920212765957447</v>
+        <v>0.2</v>
       </c>
       <c r="W5">
-        <v>-0.02669039145907473</v>
-      </c>
-      <c r="X5">
-        <v>0.06072813889281154</v>
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y5">
-        <v>-0.08741853035188628</v>
+        <v>46.81283658587657</v>
       </c>
       <c r="Z5">
-        <v>2.786421499292786</v>
-      </c>
-      <c r="AA5">
-        <v>-0.1084865629420085</v>
-      </c>
-      <c r="AB5">
-        <v>0.05252087757475747</v>
-      </c>
-      <c r="AC5">
-        <v>-0.161007440516766</v>
-      </c>
-      <c r="AD5">
-        <v>5.19</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>5.19</v>
-      </c>
-      <c r="AG5">
-        <v>-4.06</v>
-      </c>
-      <c r="AH5">
-        <v>0.2163401417257191</v>
-      </c>
-      <c r="AI5">
-        <v>0.3830258302583026</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.2754409769335142</v>
-      </c>
-      <c r="AK5">
-        <v>-0.9441860465116279</v>
-      </c>
-      <c r="AL5">
-        <v>0.079</v>
-      </c>
-      <c r="AM5">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AN5">
-        <v>-9.33453237410072</v>
-      </c>
-      <c r="AO5">
-        <v>-9.708860759493671</v>
-      </c>
-      <c r="AP5">
-        <v>7.302158273381294</v>
-      </c>
-      <c r="AQ5">
-        <v>-10.65277777777778</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09038467238521736</v>
+      </c>
+      <c r="C6">
+        <v>22.32243930862499</v>
+      </c>
+      <c r="D6">
+        <v>18.40483930862499</v>
+      </c>
+      <c r="E6">
+        <v>-0.9376000000000001</v>
+      </c>
+      <c r="F6">
+        <v>0.9224</v>
+      </c>
+      <c r="G6">
+        <v>4.84</v>
+      </c>
+      <c r="H6">
+        <v>21.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.65</v>
+      </c>
+      <c r="K6">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L6">
+        <v>1.48</v>
+      </c>
+      <c r="M6">
+        <v>0.04215368000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.43784632</v>
+      </c>
+      <c r="O6">
+        <v>0.2875692639999999</v>
+      </c>
+      <c r="P6">
+        <v>1.150277056</v>
+      </c>
+      <c r="Q6">
+        <v>1.320277056</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09262736706793474</v>
+      </c>
+      <c r="T6">
+        <v>0.7746263459859422</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>35.10962743940742</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09025809038444067</v>
+      </c>
+      <c r="C7">
+        <v>22.13424076200046</v>
+      </c>
+      <c r="D7">
+        <v>18.44724076200045</v>
+      </c>
+      <c r="E7">
+        <v>-0.7070000000000001</v>
+      </c>
+      <c r="F7">
+        <v>1.153</v>
+      </c>
+      <c r="G7">
+        <v>4.84</v>
+      </c>
+      <c r="H7">
+        <v>21.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.65</v>
+      </c>
+      <c r="K7">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L7">
+        <v>1.48</v>
+      </c>
+      <c r="M7">
+        <v>0.05269210000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.4273079</v>
+      </c>
+      <c r="O7">
+        <v>0.2854615799999999</v>
+      </c>
+      <c r="P7">
+        <v>1.14184632</v>
+      </c>
+      <c r="Q7">
+        <v>1.31184632</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0930843056678323</v>
+      </c>
+      <c r="T7">
+        <v>0.7812021214187598</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>28.08770195152594</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09013150838366406</v>
+      </c>
+      <c r="C8">
+        <v>21.94623803722293</v>
+      </c>
+      <c r="D8">
+        <v>18.48983803722293</v>
+      </c>
+      <c r="E8">
+        <v>-0.4764000000000002</v>
+      </c>
+      <c r="F8">
+        <v>1.3836</v>
+      </c>
+      <c r="G8">
+        <v>4.84</v>
+      </c>
+      <c r="H8">
+        <v>21.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.65</v>
+      </c>
+      <c r="K8">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L8">
+        <v>1.48</v>
+      </c>
+      <c r="M8">
+        <v>0.06323052</v>
+      </c>
+      <c r="N8">
+        <v>1.41676948</v>
+      </c>
+      <c r="O8">
+        <v>0.2833538959999999</v>
+      </c>
+      <c r="P8">
+        <v>1.133415584</v>
+      </c>
+      <c r="Q8">
+        <v>1.303415584</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09355096636560006</v>
+      </c>
+      <c r="T8">
+        <v>0.7879178069671696</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.40641829293828</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.0900049263828874</v>
+      </c>
+      <c r="C9">
+        <v>21.75843249397274</v>
+      </c>
+      <c r="D9">
+        <v>18.53263249397274</v>
+      </c>
+      <c r="E9">
+        <v>-0.2458</v>
+      </c>
+      <c r="F9">
+        <v>1.6142</v>
+      </c>
+      <c r="G9">
+        <v>4.84</v>
+      </c>
+      <c r="H9">
+        <v>21.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.65</v>
+      </c>
+      <c r="K9">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L9">
+        <v>1.48</v>
+      </c>
+      <c r="M9">
+        <v>0.07376894000000001</v>
+      </c>
+      <c r="N9">
+        <v>1.40623106</v>
+      </c>
+      <c r="O9">
+        <v>0.2812462119999999</v>
+      </c>
+      <c r="P9">
+        <v>1.124984848</v>
+      </c>
+      <c r="Q9">
+        <v>1.294984848</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09402766277729829</v>
+      </c>
+      <c r="T9">
+        <v>0.7947779158607065</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>20.06264425108996</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08987834438211076</v>
+      </c>
+      <c r="C10">
+        <v>21.57082550454724</v>
+      </c>
+      <c r="D10">
+        <v>18.57562550454724</v>
+      </c>
+      <c r="E10">
+        <v>-0.0152000000000001</v>
+      </c>
+      <c r="F10">
+        <v>1.8448</v>
+      </c>
+      <c r="G10">
+        <v>4.84</v>
+      </c>
+      <c r="H10">
+        <v>21.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.65</v>
+      </c>
+      <c r="K10">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.48</v>
+      </c>
+      <c r="M10">
+        <v>0.08430736000000001</v>
+      </c>
+      <c r="N10">
+        <v>1.39569264</v>
+      </c>
+      <c r="O10">
+        <v>0.2791385279999999</v>
+      </c>
+      <c r="P10">
+        <v>1.116554112</v>
+      </c>
+      <c r="Q10">
+        <v>1.286554112</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09451472215446821</v>
+      </c>
+      <c r="T10">
+        <v>0.8017871575562766</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03656</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.55481371970371</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08975176238133412</v>
+      </c>
+      <c r="C11">
+        <v>21.38341845400751</v>
+      </c>
+      <c r="D11">
+        <v>18.61881845400751</v>
+      </c>
+      <c r="E11">
+        <v>0.2153999999999996</v>
+      </c>
+      <c r="F11">
+        <v>2.0754</v>
+      </c>
+      <c r="G11">
+        <v>4.84</v>
+      </c>
+      <c r="H11">
+        <v>21.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.65</v>
+      </c>
+      <c r="K11">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L11">
+        <v>1.48</v>
+      </c>
+      <c r="M11">
+        <v>0.09484577999999999</v>
+      </c>
+      <c r="N11">
+        <v>1.38515422</v>
+      </c>
+      <c r="O11">
+        <v>0.2770308439999999</v>
+      </c>
+      <c r="P11">
+        <v>1.108123376</v>
+      </c>
+      <c r="Q11">
+        <v>1.278123376</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09501248613333418</v>
+      </c>
+      <c r="T11">
+        <v>0.8089504485198813</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03656</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.60427886195886</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08962518038055747</v>
+      </c>
+      <c r="C12">
+        <v>21.19621274032708</v>
+      </c>
+      <c r="D12">
+        <v>18.66221274032709</v>
+      </c>
+      <c r="E12">
+        <v>0.446</v>
+      </c>
+      <c r="F12">
+        <v>2.306</v>
+      </c>
+      <c r="G12">
+        <v>4.84</v>
+      </c>
+      <c r="H12">
+        <v>21.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.65</v>
+      </c>
+      <c r="K12">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L12">
+        <v>1.48</v>
+      </c>
+      <c r="M12">
+        <v>0.1053842</v>
+      </c>
+      <c r="N12">
+        <v>1.3746158</v>
+      </c>
+      <c r="O12">
+        <v>0.2749231599999999</v>
+      </c>
+      <c r="P12">
+        <v>1.09969264</v>
+      </c>
+      <c r="Q12">
+        <v>1.26969264</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09552131153395274</v>
+      </c>
+      <c r="T12">
+        <v>0.8162729237271218</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03656</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>14.04385097576297</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08963939837978081</v>
+      </c>
+      <c r="C13">
+        <v>20.96072850678791</v>
+      </c>
+      <c r="D13">
+        <v>18.65732850678791</v>
+      </c>
+      <c r="E13">
+        <v>0.6765999999999999</v>
+      </c>
+      <c r="F13">
+        <v>2.5366</v>
+      </c>
+      <c r="G13">
+        <v>4.84</v>
+      </c>
+      <c r="H13">
+        <v>21.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.65</v>
+      </c>
+      <c r="K13">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L13">
+        <v>1.48</v>
+      </c>
+      <c r="M13">
+        <v>0.11998118</v>
+      </c>
+      <c r="N13">
+        <v>1.36001882</v>
+      </c>
+      <c r="O13">
+        <v>0.272003764</v>
+      </c>
+      <c r="P13">
+        <v>1.088015056</v>
+      </c>
+      <c r="Q13">
+        <v>1.258015056</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09604157121323686</v>
+      </c>
+      <c r="T13">
+        <v>0.8237599489390192</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.33526791451793</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.08952561637900416</v>
+      </c>
+      <c r="C14">
+        <v>20.76928721734884</v>
+      </c>
+      <c r="D14">
+        <v>18.69648721734884</v>
+      </c>
+      <c r="E14">
+        <v>0.9071999999999998</v>
+      </c>
+      <c r="F14">
+        <v>2.7672</v>
+      </c>
+      <c r="G14">
+        <v>4.84</v>
+      </c>
+      <c r="H14">
+        <v>21.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.65</v>
+      </c>
+      <c r="K14">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L14">
+        <v>1.48</v>
+      </c>
+      <c r="M14">
+        <v>0.13088856</v>
+      </c>
+      <c r="N14">
+        <v>1.34911144</v>
+      </c>
+      <c r="O14">
+        <v>0.2698222879999999</v>
+      </c>
+      <c r="P14">
+        <v>1.079289152</v>
+      </c>
+      <c r="Q14">
+        <v>1.249289152</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09657365497614109</v>
+      </c>
+      <c r="T14">
+        <v>0.8314171338148234</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.30732892164143</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.08941183437822751</v>
+      </c>
+      <c r="C15">
+        <v>20.57801064921477</v>
+      </c>
+      <c r="D15">
+        <v>18.73581064921477</v>
+      </c>
+      <c r="E15">
+        <v>1.1378</v>
+      </c>
+      <c r="F15">
+        <v>2.9978</v>
+      </c>
+      <c r="G15">
+        <v>4.84</v>
+      </c>
+      <c r="H15">
+        <v>21.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.65</v>
+      </c>
+      <c r="K15">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L15">
+        <v>1.48</v>
+      </c>
+      <c r="M15">
+        <v>0.14179594</v>
+      </c>
+      <c r="N15">
+        <v>1.33820406</v>
+      </c>
+      <c r="O15">
+        <v>0.267640812</v>
+      </c>
+      <c r="P15">
+        <v>1.070563248</v>
+      </c>
+      <c r="Q15">
+        <v>1.240563248</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09711797054968679</v>
+      </c>
+      <c r="T15">
+        <v>0.8392503459291518</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.43753438920748</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.08972365237745086</v>
+      </c>
+      <c r="C16">
+        <v>20.24003756186579</v>
+      </c>
+      <c r="D16">
+        <v>18.62843756186579</v>
+      </c>
+      <c r="E16">
+        <v>1.3684</v>
+      </c>
+      <c r="F16">
+        <v>3.2284</v>
+      </c>
+      <c r="G16">
+        <v>4.84</v>
+      </c>
+      <c r="H16">
+        <v>21.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.65</v>
+      </c>
+      <c r="K16">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L16">
+        <v>1.48</v>
+      </c>
+      <c r="M16">
+        <v>0.16497124</v>
+      </c>
+      <c r="N16">
+        <v>1.31502876</v>
+      </c>
+      <c r="O16">
+        <v>0.2630057519999999</v>
+      </c>
+      <c r="P16">
+        <v>1.052023008</v>
+      </c>
+      <c r="Q16">
+        <v>1.222023008</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09767494462494286</v>
+      </c>
+      <c r="T16">
+        <v>0.8472657257670694</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.04088</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.971260687620459</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.08964027037667421</v>
+      </c>
+      <c r="C17">
+        <v>20.03802903754501</v>
+      </c>
+      <c r="D17">
+        <v>18.657029037545</v>
+      </c>
+      <c r="E17">
+        <v>1.599</v>
+      </c>
+      <c r="F17">
+        <v>3.459</v>
+      </c>
+      <c r="G17">
+        <v>4.84</v>
+      </c>
+      <c r="H17">
+        <v>21.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.65</v>
+      </c>
+      <c r="K17">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L17">
+        <v>1.48</v>
+      </c>
+      <c r="M17">
+        <v>0.1767549</v>
+      </c>
+      <c r="N17">
+        <v>1.3032451</v>
+      </c>
+      <c r="O17">
+        <v>0.26064902</v>
+      </c>
+      <c r="P17">
+        <v>1.04259608</v>
+      </c>
+      <c r="Q17">
+        <v>1.21259608</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.0982450239725579</v>
+      </c>
+      <c r="T17">
+        <v>0.8554697027776437</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.04088</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.373176641779096</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08955688837589756</v>
+      </c>
+      <c r="C18">
+        <v>19.83610841421843</v>
+      </c>
+      <c r="D18">
+        <v>18.68570841421842</v>
+      </c>
+      <c r="E18">
+        <v>1.8296</v>
+      </c>
+      <c r="F18">
+        <v>3.6896</v>
+      </c>
+      <c r="G18">
+        <v>4.84</v>
+      </c>
+      <c r="H18">
+        <v>21.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.65</v>
+      </c>
+      <c r="K18">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L18">
+        <v>1.48</v>
+      </c>
+      <c r="M18">
+        <v>0.18853856</v>
+      </c>
+      <c r="N18">
+        <v>1.29146144</v>
+      </c>
+      <c r="O18">
+        <v>0.2582922879999999</v>
+      </c>
+      <c r="P18">
+        <v>1.033169152</v>
+      </c>
+      <c r="Q18">
+        <v>1.203169152</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09882867663797329</v>
+      </c>
+      <c r="T18">
+        <v>0.8638690125741841</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.04088</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.849853101667903</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08973190637512092</v>
+      </c>
+      <c r="C19">
+        <v>19.54541205305135</v>
+      </c>
+      <c r="D19">
+        <v>18.62561205305136</v>
+      </c>
+      <c r="E19">
+        <v>2.0602</v>
+      </c>
+      <c r="F19">
+        <v>3.9202</v>
+      </c>
+      <c r="G19">
+        <v>4.84</v>
+      </c>
+      <c r="H19">
+        <v>21.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.65</v>
+      </c>
+      <c r="K19">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L19">
+        <v>1.48</v>
+      </c>
+      <c r="M19">
+        <v>0.2077706</v>
+      </c>
+      <c r="N19">
+        <v>1.2722294</v>
+      </c>
+      <c r="O19">
+        <v>0.25444588</v>
+      </c>
+      <c r="P19">
+        <v>1.01778352</v>
+      </c>
+      <c r="Q19">
+        <v>1.18778352</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09942639322303726</v>
+      </c>
+      <c r="T19">
+        <v>0.8724707153778701</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.123240727995202</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.08966372437434428</v>
+      </c>
+      <c r="C20">
+        <v>19.33817785377833</v>
+      </c>
+      <c r="D20">
+        <v>18.64897785377833</v>
+      </c>
+      <c r="E20">
+        <v>2.290799999999999</v>
+      </c>
+      <c r="F20">
+        <v>4.150799999999999</v>
+      </c>
+      <c r="G20">
+        <v>4.84</v>
+      </c>
+      <c r="H20">
+        <v>21.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.65</v>
+      </c>
+      <c r="K20">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L20">
+        <v>1.48</v>
+      </c>
+      <c r="M20">
+        <v>0.2199924</v>
+      </c>
+      <c r="N20">
+        <v>1.2600076</v>
+      </c>
+      <c r="O20">
+        <v>0.2520015199999999</v>
+      </c>
+      <c r="P20">
+        <v>1.00800608</v>
+      </c>
+      <c r="Q20">
+        <v>1.17800608</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1000386882613954</v>
+      </c>
+      <c r="T20">
+        <v>0.8812822158109144</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.72750513199547</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.08959554237356765</v>
+      </c>
+      <c r="C21">
+        <v>19.13100235286206</v>
+      </c>
+      <c r="D21">
+        <v>18.67240235286206</v>
+      </c>
+      <c r="E21">
+        <v>2.5214</v>
+      </c>
+      <c r="F21">
+        <v>4.3814</v>
+      </c>
+      <c r="G21">
+        <v>4.84</v>
+      </c>
+      <c r="H21">
+        <v>21.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.65</v>
+      </c>
+      <c r="K21">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L21">
+        <v>1.48</v>
+      </c>
+      <c r="M21">
+        <v>0.2322142</v>
+      </c>
+      <c r="N21">
+        <v>1.2477858</v>
+      </c>
+      <c r="O21">
+        <v>0.2495571599999999</v>
+      </c>
+      <c r="P21">
+        <v>0.99822864</v>
+      </c>
+      <c r="Q21">
+        <v>1.16822864</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1006661016957625</v>
+      </c>
+      <c r="T21">
+        <v>0.8903112841558857</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.373425914522022</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.08984736037279098</v>
+      </c>
+      <c r="C22">
+        <v>18.81417949092932</v>
+      </c>
+      <c r="D22">
+        <v>18.58617949092932</v>
+      </c>
+      <c r="E22">
+        <v>2.752</v>
+      </c>
+      <c r="F22">
+        <v>4.612</v>
+      </c>
+      <c r="G22">
+        <v>4.84</v>
+      </c>
+      <c r="H22">
+        <v>21.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.65</v>
+      </c>
+      <c r="K22">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L22">
+        <v>1.48</v>
+      </c>
+      <c r="M22">
+        <v>0.25366</v>
+      </c>
+      <c r="N22">
+        <v>1.22634</v>
+      </c>
+      <c r="O22">
+        <v>0.2452679999999999</v>
+      </c>
+      <c r="P22">
+        <v>0.9810720000000001</v>
+      </c>
+      <c r="Q22">
+        <v>1.151072</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1013092004659887</v>
+      </c>
+      <c r="T22">
+        <v>0.8995660792094811</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.044</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.83458172356698</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.08979517837201434</v>
+      </c>
+      <c r="C23">
+        <v>18.60138121590757</v>
+      </c>
+      <c r="D23">
+        <v>18.60398121590756</v>
+      </c>
+      <c r="E23">
+        <v>2.982599999999999</v>
+      </c>
+      <c r="F23">
+        <v>4.842599999999999</v>
+      </c>
+      <c r="G23">
+        <v>4.84</v>
+      </c>
+      <c r="H23">
+        <v>21.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.65</v>
+      </c>
+      <c r="K23">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L23">
+        <v>1.48</v>
+      </c>
+      <c r="M23">
+        <v>0.2663429999999999</v>
+      </c>
+      <c r="N23">
+        <v>1.213657</v>
+      </c>
+      <c r="O23">
+        <v>0.2427313999999999</v>
+      </c>
+      <c r="P23">
+        <v>0.9709256000000001</v>
+      </c>
+      <c r="Q23">
+        <v>1.1409256</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1019685802177397</v>
+      </c>
+      <c r="T23">
+        <v>0.9090551728720283</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.044</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.556744498635219</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.08974299637123767</v>
+      </c>
+      <c r="C24">
+        <v>18.38861707433745</v>
+      </c>
+      <c r="D24">
+        <v>18.62181707433745</v>
+      </c>
+      <c r="E24">
+        <v>3.2132</v>
+      </c>
+      <c r="F24">
+        <v>5.0732</v>
+      </c>
+      <c r="G24">
+        <v>4.84</v>
+      </c>
+      <c r="H24">
+        <v>21.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.65</v>
+      </c>
+      <c r="K24">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L24">
+        <v>1.48</v>
+      </c>
+      <c r="M24">
+        <v>0.279026</v>
+      </c>
+      <c r="N24">
+        <v>1.200974</v>
+      </c>
+      <c r="O24">
+        <v>0.2401947999999999</v>
+      </c>
+      <c r="P24">
+        <v>0.9607792000000001</v>
+      </c>
+      <c r="Q24">
+        <v>1.1307792</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1026448671426124</v>
+      </c>
+      <c r="T24">
+        <v>0.9187875766284871</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.044</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.304165203242708</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.08969081437046104</v>
+      </c>
+      <c r="C25">
+        <v>18.17588716448561</v>
+      </c>
+      <c r="D25">
+        <v>18.63968716448561</v>
+      </c>
+      <c r="E25">
+        <v>3.4438</v>
+      </c>
+      <c r="F25">
+        <v>5.3038</v>
+      </c>
+      <c r="G25">
+        <v>4.84</v>
+      </c>
+      <c r="H25">
+        <v>21.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.65</v>
+      </c>
+      <c r="K25">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L25">
+        <v>1.48</v>
+      </c>
+      <c r="M25">
+        <v>0.291709</v>
+      </c>
+      <c r="N25">
+        <v>1.188291</v>
+      </c>
+      <c r="O25">
+        <v>0.2376581999999999</v>
+      </c>
+      <c r="P25">
+        <v>0.9506328000000001</v>
+      </c>
+      <c r="Q25">
+        <v>1.1206328</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1033387199616377</v>
+      </c>
+      <c r="T25">
+        <v>0.9287727700929058</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.044</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.073549324840852</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.08963863236968439</v>
+      </c>
+      <c r="C26">
+        <v>17.96319158499627</v>
+      </c>
+      <c r="D26">
+        <v>18.65759158499627</v>
+      </c>
+      <c r="E26">
+        <v>3.674399999999999</v>
+      </c>
+      <c r="F26">
+        <v>5.5344</v>
+      </c>
+      <c r="G26">
+        <v>4.84</v>
+      </c>
+      <c r="H26">
+        <v>21.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.65</v>
+      </c>
+      <c r="K26">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L26">
+        <v>1.48</v>
+      </c>
+      <c r="M26">
+        <v>0.304392</v>
+      </c>
+      <c r="N26">
+        <v>1.175608</v>
+      </c>
+      <c r="O26">
+        <v>0.2351216</v>
+      </c>
+      <c r="P26">
+        <v>0.9404864000000001</v>
+      </c>
+      <c r="Q26">
+        <v>1.1104864</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1040508320653742</v>
+      </c>
+      <c r="T26">
+        <v>0.939020731806388</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.044</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.862151436305816</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.08958645036890774</v>
+      </c>
+      <c r="C27">
+        <v>17.75053043489301</v>
+      </c>
+      <c r="D27">
+        <v>18.67553043489301</v>
+      </c>
+      <c r="E27">
+        <v>3.904999999999999</v>
+      </c>
+      <c r="F27">
+        <v>5.765</v>
+      </c>
+      <c r="G27">
+        <v>4.84</v>
+      </c>
+      <c r="H27">
+        <v>21.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.65</v>
+      </c>
+      <c r="K27">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L27">
+        <v>1.48</v>
+      </c>
+      <c r="M27">
+        <v>0.317075</v>
+      </c>
+      <c r="N27">
+        <v>1.162925</v>
+      </c>
+      <c r="O27">
+        <v>0.232585</v>
+      </c>
+      <c r="P27">
+        <v>0.9303400000000001</v>
+      </c>
+      <c r="Q27">
+        <v>1.10034</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1047819338252103</v>
+      </c>
+      <c r="T27">
+        <v>0.9495419724988966</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.044</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.667665378853584</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09032466836813109</v>
+      </c>
+      <c r="C28">
+        <v>17.26931466123725</v>
+      </c>
+      <c r="D28">
+        <v>18.42491466123725</v>
+      </c>
+      <c r="E28">
+        <v>4.135599999999999</v>
+      </c>
+      <c r="F28">
+        <v>5.9956</v>
+      </c>
+      <c r="G28">
+        <v>4.84</v>
+      </c>
+      <c r="H28">
+        <v>21.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.65</v>
+      </c>
+      <c r="K28">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L28">
+        <v>1.48</v>
+      </c>
+      <c r="M28">
+        <v>0.35254128</v>
+      </c>
+      <c r="N28">
+        <v>1.12745872</v>
+      </c>
+      <c r="O28">
+        <v>0.2254917439999999</v>
+      </c>
+      <c r="P28">
+        <v>0.901966976</v>
+      </c>
+      <c r="Q28">
+        <v>1.071966976</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.105532795092069</v>
+      </c>
+      <c r="T28">
+        <v>0.9603475710479595</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.198089937155729</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09030288636735445</v>
+      </c>
+      <c r="C29">
+        <v>17.04601303459551</v>
+      </c>
+      <c r="D29">
+        <v>18.43221303459551</v>
+      </c>
+      <c r="E29">
+        <v>4.3662</v>
+      </c>
+      <c r="F29">
+        <v>6.2262</v>
+      </c>
+      <c r="G29">
+        <v>4.84</v>
+      </c>
+      <c r="H29">
+        <v>21.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.65</v>
+      </c>
+      <c r="K29">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L29">
+        <v>1.48</v>
+      </c>
+      <c r="M29">
+        <v>0.3661005600000001</v>
+      </c>
+      <c r="N29">
+        <v>1.11389944</v>
+      </c>
+      <c r="O29">
+        <v>0.222779888</v>
+      </c>
+      <c r="P29">
+        <v>0.891119552</v>
+      </c>
+      <c r="Q29">
+        <v>1.061119552</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1063042279004855</v>
+      </c>
+      <c r="T29">
+        <v>0.9714492133928871</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.042605124668478</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09122190436657779</v>
+      </c>
+      <c r="C30">
+        <v>16.51242458788417</v>
+      </c>
+      <c r="D30">
+        <v>18.12922458788417</v>
+      </c>
+      <c r="E30">
+        <v>4.5968</v>
+      </c>
+      <c r="F30">
+        <v>6.4568</v>
+      </c>
+      <c r="G30">
+        <v>4.84</v>
+      </c>
+      <c r="H30">
+        <v>21.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.65</v>
+      </c>
+      <c r="K30">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L30">
+        <v>1.48</v>
+      </c>
+      <c r="M30">
+        <v>0.4067784</v>
+      </c>
+      <c r="N30">
+        <v>1.0732216</v>
+      </c>
+      <c r="O30">
+        <v>0.2146443199999999</v>
+      </c>
+      <c r="P30">
+        <v>0.85857728</v>
+      </c>
+      <c r="Q30">
+        <v>1.02857728</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1070970893980247</v>
+      </c>
+      <c r="T30">
+        <v>0.9828592346918404</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.0504</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.638344612201631</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09123372236580114</v>
+      </c>
+      <c r="C31">
+        <v>16.27799320139018</v>
+      </c>
+      <c r="D31">
+        <v>18.12539320139018</v>
+      </c>
+      <c r="E31">
+        <v>4.827399999999999</v>
+      </c>
+      <c r="F31">
+        <v>6.687399999999999</v>
+      </c>
+      <c r="G31">
+        <v>4.84</v>
+      </c>
+      <c r="H31">
+        <v>21.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.65</v>
+      </c>
+      <c r="K31">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L31">
+        <v>1.48</v>
+      </c>
+      <c r="M31">
+        <v>0.4213062</v>
+      </c>
+      <c r="N31">
+        <v>1.0586938</v>
+      </c>
+      <c r="O31">
+        <v>0.2117387599999999</v>
+      </c>
+      <c r="P31">
+        <v>0.84695504</v>
+      </c>
+      <c r="Q31">
+        <v>1.01695504</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1079122850222551</v>
+      </c>
+      <c r="T31">
+        <v>0.9945906650414685</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.0504</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.512884453160196</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09294954036502451</v>
+      </c>
+      <c r="C32">
+        <v>15.50780041268189</v>
+      </c>
+      <c r="D32">
+        <v>17.58580041268189</v>
+      </c>
+      <c r="E32">
+        <v>5.057999999999999</v>
+      </c>
+      <c r="F32">
+        <v>6.917999999999999</v>
+      </c>
+      <c r="G32">
+        <v>4.84</v>
+      </c>
+      <c r="H32">
+        <v>21.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.65</v>
+      </c>
+      <c r="K32">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L32">
+        <v>1.48</v>
+      </c>
+      <c r="M32">
+        <v>0.4849517999999999</v>
+      </c>
+      <c r="N32">
+        <v>0.9950482</v>
+      </c>
+      <c r="O32">
+        <v>0.19900964</v>
+      </c>
+      <c r="P32">
+        <v>0.7960385600000001</v>
+      </c>
+      <c r="Q32">
+        <v>0.96603856</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.108750771950035</v>
+      </c>
+      <c r="T32">
+        <v>1.006657279115372</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.05608</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.0518496889794</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09830055836424785</v>
+      </c>
+      <c r="C33">
+        <v>13.78320692022221</v>
+      </c>
+      <c r="D33">
+        <v>16.09180692022221</v>
+      </c>
+      <c r="E33">
+        <v>5.288599999999999</v>
+      </c>
+      <c r="F33">
+        <v>7.148599999999999</v>
+      </c>
+      <c r="G33">
+        <v>4.84</v>
+      </c>
+      <c r="H33">
+        <v>21.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.65</v>
+      </c>
+      <c r="K33">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L33">
+        <v>1.48</v>
+      </c>
+      <c r="M33">
+        <v>0.65338204</v>
+      </c>
+      <c r="N33">
+        <v>0.82661796</v>
+      </c>
+      <c r="O33">
+        <v>0.165323592</v>
+      </c>
+      <c r="P33">
+        <v>0.6612943680000001</v>
+      </c>
+      <c r="Q33">
+        <v>0.831294368</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.109613562846736</v>
+      </c>
+      <c r="T33">
+        <v>1.019073650118953</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.07312</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.265137254155318</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.0985395763634712</v>
+      </c>
+      <c r="C34">
+        <v>13.4917737201201</v>
+      </c>
+      <c r="D34">
+        <v>16.0309737201201</v>
+      </c>
+      <c r="E34">
+        <v>5.5192</v>
+      </c>
+      <c r="F34">
+        <v>7.3792</v>
+      </c>
+      <c r="G34">
+        <v>4.84</v>
+      </c>
+      <c r="H34">
+        <v>21.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.65</v>
+      </c>
+      <c r="K34">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L34">
+        <v>1.48</v>
+      </c>
+      <c r="M34">
+        <v>0.6744588800000001</v>
+      </c>
+      <c r="N34">
+        <v>0.8055411199999999</v>
+      </c>
+      <c r="O34">
+        <v>0.1611082239999999</v>
+      </c>
+      <c r="P34">
+        <v>0.644432896</v>
+      </c>
+      <c r="Q34">
+        <v>0.8144328959999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1105017299462812</v>
+      </c>
+      <c r="T34">
+        <v>1.031855208504993</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.07312</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.194351714962964</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09877859436269455</v>
+      </c>
+      <c r="C35">
+        <v>13.20079873343786</v>
+      </c>
+      <c r="D35">
+        <v>15.97059873343786</v>
+      </c>
+      <c r="E35">
+        <v>5.7498</v>
+      </c>
+      <c r="F35">
+        <v>7.6098</v>
+      </c>
+      <c r="G35">
+        <v>4.84</v>
+      </c>
+      <c r="H35">
+        <v>21.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.65</v>
+      </c>
+      <c r="K35">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L35">
+        <v>1.48</v>
+      </c>
+      <c r="M35">
+        <v>0.6955357200000001</v>
+      </c>
+      <c r="N35">
+        <v>0.7844642799999999</v>
+      </c>
+      <c r="O35">
+        <v>0.1568928559999999</v>
+      </c>
+      <c r="P35">
+        <v>0.627571424</v>
+      </c>
+      <c r="Q35">
+        <v>0.7975714239999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1114164094965591</v>
+      </c>
+      <c r="T35">
+        <v>1.045018305947333</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.07312</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.127856208448935</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.0990176123619179</v>
+      </c>
+      <c r="C36">
+        <v>12.91027680250417</v>
+      </c>
+      <c r="D36">
+        <v>15.91067680250417</v>
+      </c>
+      <c r="E36">
+        <v>5.980399999999999</v>
+      </c>
+      <c r="F36">
+        <v>7.8404</v>
+      </c>
+      <c r="G36">
+        <v>4.84</v>
+      </c>
+      <c r="H36">
+        <v>21.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.65</v>
+      </c>
+      <c r="K36">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L36">
+        <v>1.48</v>
+      </c>
+      <c r="M36">
+        <v>0.7166125600000001</v>
+      </c>
+      <c r="N36">
+        <v>0.7633874399999999</v>
+      </c>
+      <c r="O36">
+        <v>0.1526774879999999</v>
+      </c>
+      <c r="P36">
+        <v>0.610709952</v>
+      </c>
+      <c r="Q36">
+        <v>0.7807099519999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1123588066089665</v>
+      </c>
+      <c r="T36">
+        <v>1.058580285130349</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.07312</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.065272202318083</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09925663036114125</v>
+      </c>
+      <c r="C37">
+        <v>12.62020284676505</v>
+      </c>
+      <c r="D37">
+        <v>15.85120284676505</v>
+      </c>
+      <c r="E37">
+        <v>6.210999999999999</v>
+      </c>
+      <c r="F37">
+        <v>8.071</v>
+      </c>
+      <c r="G37">
+        <v>4.84</v>
+      </c>
+      <c r="H37">
+        <v>21.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.65</v>
+      </c>
+      <c r="K37">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L37">
+        <v>1.48</v>
+      </c>
+      <c r="M37">
+        <v>0.7376894000000001</v>
+      </c>
+      <c r="N37">
+        <v>0.7423105999999999</v>
+      </c>
+      <c r="O37">
+        <v>0.1484621199999999</v>
+      </c>
+      <c r="P37">
+        <v>0.59384848</v>
+      </c>
+      <c r="Q37">
+        <v>0.7638484799999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1133302005556019</v>
+      </c>
+      <c r="T37">
+        <v>1.072559555980535</v>
+      </c>
+      <c r="U37">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.07312</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>2.006264425108996</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1055724483603646</v>
+      </c>
+      <c r="C38">
+        <v>10.96467946658331</v>
+      </c>
+      <c r="D38">
+        <v>14.42627946658331</v>
+      </c>
+      <c r="E38">
+        <v>6.441599999999998</v>
+      </c>
+      <c r="F38">
+        <v>8.301599999999999</v>
+      </c>
+      <c r="G38">
+        <v>4.84</v>
+      </c>
+      <c r="H38">
+        <v>21.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.65</v>
+      </c>
+      <c r="K38">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L38">
+        <v>1.48</v>
+      </c>
+      <c r="M38">
+        <v>0.9339299999999999</v>
+      </c>
+      <c r="N38">
+        <v>0.5460700000000001</v>
+      </c>
+      <c r="O38">
+        <v>0.109214</v>
+      </c>
+      <c r="P38">
+        <v>0.4368560000000001</v>
+      </c>
+      <c r="Q38">
+        <v>0.6068560000000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1143319505630697</v>
+      </c>
+      <c r="T38">
+        <v>1.08697567904479</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.584701208870044</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.105980266359588</v>
+      </c>
+      <c r="C39">
+        <v>10.65082513634556</v>
+      </c>
+      <c r="D39">
+        <v>14.34302513634556</v>
+      </c>
+      <c r="E39">
+        <v>6.672199999999999</v>
+      </c>
+      <c r="F39">
+        <v>8.5322</v>
+      </c>
+      <c r="G39">
+        <v>4.84</v>
+      </c>
+      <c r="H39">
+        <v>21.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.65</v>
+      </c>
+      <c r="K39">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L39">
+        <v>1.48</v>
+      </c>
+      <c r="M39">
+        <v>0.9598725</v>
+      </c>
+      <c r="N39">
+        <v>0.5201275</v>
+      </c>
+      <c r="O39">
+        <v>0.1040255</v>
+      </c>
+      <c r="P39">
+        <v>0.416102</v>
+      </c>
+      <c r="Q39">
+        <v>0.5861019999999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1153655021580761</v>
+      </c>
+      <c r="T39">
+        <v>1.101849456809497</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.541871446468151</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1063880843588113</v>
+      </c>
+      <c r="C40">
+        <v>10.33792621702595</v>
+      </c>
+      <c r="D40">
+        <v>14.26072621702595</v>
+      </c>
+      <c r="E40">
+        <v>6.9028</v>
+      </c>
+      <c r="F40">
+        <v>8.7628</v>
+      </c>
+      <c r="G40">
+        <v>4.84</v>
+      </c>
+      <c r="H40">
+        <v>21.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.65</v>
+      </c>
+      <c r="K40">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L40">
+        <v>1.48</v>
+      </c>
+      <c r="M40">
+        <v>0.9858150000000001</v>
+      </c>
+      <c r="N40">
+        <v>0.4941849999999999</v>
+      </c>
+      <c r="O40">
+        <v>0.09883699999999995</v>
+      </c>
+      <c r="P40">
+        <v>0.3953479999999999</v>
+      </c>
+      <c r="Q40">
+        <v>0.5653479999999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.116432394127115</v>
+      </c>
+      <c r="T40">
+        <v>1.117203033856936</v>
+      </c>
+      <c r="U40">
+        <v>0.1125</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>1.50129588208741</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1361958817489604</v>
+      </c>
+      <c r="C41">
+        <v>5.893689157425717</v>
+      </c>
+      <c r="D41">
+        <v>10.04708915742572</v>
+      </c>
+      <c r="E41">
+        <v>7.133399999999999</v>
+      </c>
+      <c r="F41">
+        <v>8.993399999999999</v>
+      </c>
+      <c r="G41">
+        <v>4.84</v>
+      </c>
+      <c r="H41">
+        <v>21.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.65</v>
+      </c>
+      <c r="K41">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L41">
+        <v>1.48</v>
+      </c>
+      <c r="M41">
+        <v>1.76810244</v>
+      </c>
+      <c r="N41">
+        <v>-0.2881024399999998</v>
+      </c>
+      <c r="O41">
+        <v>-0.05762048799999996</v>
+      </c>
+      <c r="P41">
+        <v>-0.2304819519999999</v>
+      </c>
+      <c r="Q41">
+        <v>-0.06048195199999995</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1186196090832914</v>
+      </c>
+      <c r="T41">
+        <v>1.148679110464035</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0.1674111144827106</v>
+      </c>
+      <c r="W41">
+        <v>0.1636869748926991</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8370555724135532</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1377738817489604</v>
+      </c>
+      <c r="C42">
+        <v>5.508352861871384</v>
+      </c>
+      <c r="D42">
+        <v>9.892352861871384</v>
+      </c>
+      <c r="E42">
+        <v>7.364</v>
+      </c>
+      <c r="F42">
+        <v>9.224</v>
+      </c>
+      <c r="G42">
+        <v>4.84</v>
+      </c>
+      <c r="H42">
+        <v>21.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.65</v>
+      </c>
+      <c r="K42">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L42">
+        <v>1.48</v>
+      </c>
+      <c r="M42">
+        <v>1.8134384</v>
+      </c>
+      <c r="N42">
+        <v>-0.3334384000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.06668768000000001</v>
+      </c>
+      <c r="P42">
+        <v>-0.2667507200000001</v>
+      </c>
+      <c r="Q42">
+        <v>-0.09675072000000018</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1199499359013463</v>
+      </c>
+      <c r="T42">
+        <v>1.167823762305102</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0.1632258366206428</v>
+      </c>
+      <c r="W42">
+        <v>0.1645098005203816</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8161291831032143</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.146677491983653</v>
+      </c>
+      <c r="C43">
+        <v>4.486852478123103</v>
+      </c>
+      <c r="D43">
+        <v>9.101452478123104</v>
+      </c>
+      <c r="E43">
+        <v>7.594600000000001</v>
+      </c>
+      <c r="F43">
+        <v>9.454600000000001</v>
+      </c>
+      <c r="G43">
+        <v>4.84</v>
+      </c>
+      <c r="H43">
+        <v>21.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.65</v>
+      </c>
+      <c r="K43">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L43">
+        <v>1.48</v>
+      </c>
+      <c r="M43">
+        <v>2.02139348</v>
+      </c>
+      <c r="N43">
+        <v>-0.54139348</v>
+      </c>
+      <c r="O43">
+        <v>-0.108278696</v>
+      </c>
+      <c r="P43">
+        <v>-0.433114784</v>
+      </c>
+      <c r="Q43">
+        <v>-0.2631147840000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1217891047042379</v>
+      </c>
+      <c r="T43">
+        <v>1.194291128015879</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1464336374529119</v>
+      </c>
+      <c r="W43">
+        <v>0.1824924883125674</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7321681872645597</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.148427491983653</v>
+      </c>
+      <c r="C44">
+        <v>4.115442558944693</v>
+      </c>
+      <c r="D44">
+        <v>8.960642558944691</v>
+      </c>
+      <c r="E44">
+        <v>7.825199999999998</v>
+      </c>
+      <c r="F44">
+        <v>9.685199999999998</v>
+      </c>
+      <c r="G44">
+        <v>4.84</v>
+      </c>
+      <c r="H44">
+        <v>21.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.65</v>
+      </c>
+      <c r="K44">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L44">
+        <v>1.48</v>
+      </c>
+      <c r="M44">
+        <v>2.07069576</v>
+      </c>
+      <c r="N44">
+        <v>-0.5906957599999996</v>
+      </c>
+      <c r="O44">
+        <v>-0.1181391519999999</v>
+      </c>
+      <c r="P44">
+        <v>-0.4725566079999997</v>
+      </c>
+      <c r="Q44">
+        <v>-0.3025566079999997</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1232199513370696</v>
+      </c>
+      <c r="T44">
+        <v>1.214882354360981</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1429471222754617</v>
+      </c>
+      <c r="W44">
+        <v>0.1832379052575063</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.7147356113773085</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.150177491983653</v>
+      </c>
+      <c r="C45">
+        <v>3.748323241458092</v>
+      </c>
+      <c r="D45">
+        <v>8.824123241458091</v>
+      </c>
+      <c r="E45">
+        <v>8.0558</v>
+      </c>
+      <c r="F45">
+        <v>9.915799999999999</v>
+      </c>
+      <c r="G45">
+        <v>4.84</v>
+      </c>
+      <c r="H45">
+        <v>21.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.65</v>
+      </c>
+      <c r="K45">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L45">
+        <v>1.48</v>
+      </c>
+      <c r="M45">
+        <v>2.11999804</v>
+      </c>
+      <c r="N45">
+        <v>-0.6399980399999996</v>
+      </c>
+      <c r="O45">
+        <v>-0.1279996079999999</v>
+      </c>
+      <c r="P45">
+        <v>-0.5119984319999997</v>
+      </c>
+      <c r="Q45">
+        <v>-0.3419984319999998</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1247010031149129</v>
+      </c>
+      <c r="T45">
+        <v>1.236196079876086</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.139622770594637</v>
+      </c>
+      <c r="W45">
+        <v>0.1839486516468666</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.698113852973185</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.151927491983653</v>
+      </c>
+      <c r="C46">
+        <v>3.385301361018382</v>
+      </c>
+      <c r="D46">
+        <v>8.691701361018382</v>
+      </c>
+      <c r="E46">
+        <v>8.2864</v>
+      </c>
+      <c r="F46">
+        <v>10.1464</v>
+      </c>
+      <c r="G46">
+        <v>4.84</v>
+      </c>
+      <c r="H46">
+        <v>21.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.65</v>
+      </c>
+      <c r="K46">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L46">
+        <v>1.48</v>
+      </c>
+      <c r="M46">
+        <v>2.16930032</v>
+      </c>
+      <c r="N46">
+        <v>-0.6893003200000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.137860064</v>
+      </c>
+      <c r="P46">
+        <v>-0.5514402560000001</v>
+      </c>
+      <c r="Q46">
+        <v>-0.3814402560000002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1262349495991078</v>
+      </c>
+      <c r="T46">
+        <v>1.258271009873873</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1364495258083952</v>
+      </c>
+      <c r="W46">
+        <v>0.1846270913821651</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6822476290419761</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.153677491983653</v>
+      </c>
+      <c r="C47">
+        <v>3.026195176682588</v>
+      </c>
+      <c r="D47">
+        <v>8.563195176682587</v>
+      </c>
+      <c r="E47">
+        <v>8.516999999999999</v>
+      </c>
+      <c r="F47">
+        <v>10.377</v>
+      </c>
+      <c r="G47">
+        <v>4.84</v>
+      </c>
+      <c r="H47">
+        <v>21.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.65</v>
+      </c>
+      <c r="K47">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L47">
+        <v>1.48</v>
+      </c>
+      <c r="M47">
+        <v>2.2186026</v>
+      </c>
+      <c r="N47">
+        <v>-0.7386025999999997</v>
+      </c>
+      <c r="O47">
+        <v>-0.1477205199999999</v>
+      </c>
+      <c r="P47">
+        <v>-0.5908820799999998</v>
+      </c>
+      <c r="Q47">
+        <v>-0.4208820799999998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1278246759554552</v>
+      </c>
+      <c r="T47">
+        <v>1.281148664598853</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1334173141237642</v>
+      </c>
+      <c r="W47">
+        <v>0.1852753782403392</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6670865706188212</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.155427491983653</v>
+      </c>
+      <c r="C48">
+        <v>2.670833539020467</v>
+      </c>
+      <c r="D48">
+        <v>8.438433539020467</v>
+      </c>
+      <c r="E48">
+        <v>8.7476</v>
+      </c>
+      <c r="F48">
+        <v>10.6076</v>
+      </c>
+      <c r="G48">
+        <v>4.84</v>
+      </c>
+      <c r="H48">
+        <v>21.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.65</v>
+      </c>
+      <c r="K48">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L48">
+        <v>1.48</v>
+      </c>
+      <c r="M48">
+        <v>2.26790488</v>
+      </c>
+      <c r="N48">
+        <v>-0.7879048799999997</v>
+      </c>
+      <c r="O48">
+        <v>-0.1575809759999999</v>
+      </c>
+      <c r="P48">
+        <v>-0.6303239039999998</v>
+      </c>
+      <c r="Q48">
+        <v>-0.4603239039999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1294732810657414</v>
+      </c>
+      <c r="T48">
+        <v>1.304873639869202</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1305169377297693</v>
+      </c>
+      <c r="W48">
+        <v>0.1858954787133753</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6525846886488468</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1571774919836531</v>
+      </c>
+      <c r="C49">
+        <v>2.319055129628182</v>
+      </c>
+      <c r="D49">
+        <v>8.317255129628183</v>
+      </c>
+      <c r="E49">
+        <v>8.978200000000001</v>
+      </c>
+      <c r="F49">
+        <v>10.8382</v>
+      </c>
+      <c r="G49">
+        <v>4.84</v>
+      </c>
+      <c r="H49">
+        <v>21.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.65</v>
+      </c>
+      <c r="K49">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L49">
+        <v>1.48</v>
+      </c>
+      <c r="M49">
+        <v>2.31720716</v>
+      </c>
+      <c r="N49">
+        <v>-0.8372071600000002</v>
+      </c>
+      <c r="O49">
+        <v>-0.167441432</v>
+      </c>
+      <c r="P49">
+        <v>-0.6697657280000002</v>
+      </c>
+      <c r="Q49">
+        <v>-0.4997657280000003</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1311840976896234</v>
+      </c>
+      <c r="T49">
+        <v>1.329493897225224</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1277399816078593</v>
+      </c>
+      <c r="W49">
+        <v>0.1864891919322397</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6386999080392968</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.158927491983653</v>
+      </c>
+      <c r="C50">
+        <v>1.970707765239192</v>
+      </c>
+      <c r="D50">
+        <v>8.199507765239192</v>
+      </c>
+      <c r="E50">
+        <v>9.2088</v>
+      </c>
+      <c r="F50">
+        <v>11.0688</v>
+      </c>
+      <c r="G50">
+        <v>4.84</v>
+      </c>
+      <c r="H50">
+        <v>21.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.65</v>
+      </c>
+      <c r="K50">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L50">
+        <v>1.48</v>
+      </c>
+      <c r="M50">
+        <v>2.36650944</v>
+      </c>
+      <c r="N50">
+        <v>-0.8865094399999998</v>
+      </c>
+      <c r="O50">
+        <v>-0.1773018879999999</v>
+      </c>
+      <c r="P50">
+        <v>-0.7092075519999999</v>
+      </c>
+      <c r="Q50">
+        <v>-0.5392075519999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1329607149528853</v>
+      </c>
+      <c r="T50">
+        <v>1.355061087556479</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.125078731991029</v>
+      </c>
+      <c r="W50">
+        <v>0.187058167100318</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.6253936599551448</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.160677491983653</v>
+      </c>
+      <c r="C51">
+        <v>1.62564776012019</v>
+      </c>
+      <c r="D51">
+        <v>8.085047760120188</v>
+      </c>
+      <c r="E51">
+        <v>9.439399999999999</v>
+      </c>
+      <c r="F51">
+        <v>11.2994</v>
+      </c>
+      <c r="G51">
+        <v>4.84</v>
+      </c>
+      <c r="H51">
+        <v>21.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.65</v>
+      </c>
+      <c r="K51">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L51">
+        <v>1.48</v>
+      </c>
+      <c r="M51">
+        <v>2.41581172</v>
+      </c>
+      <c r="N51">
+        <v>-0.9358117199999998</v>
+      </c>
+      <c r="O51">
+        <v>-0.1871623439999999</v>
+      </c>
+      <c r="P51">
+        <v>-0.7486493759999999</v>
+      </c>
+      <c r="Q51">
+        <v>-0.578649376</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1348070034813733</v>
+      </c>
+      <c r="T51">
+        <v>1.381630912802684</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.1225261048075385</v>
+      </c>
+      <c r="W51">
+        <v>0.1876039187921482</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6126305240376928</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.162427491983653</v>
+      </c>
+      <c r="C52">
+        <v>1.283739341135197</v>
+      </c>
+      <c r="D52">
+        <v>7.973739341135196</v>
+      </c>
+      <c r="E52">
+        <v>9.67</v>
+      </c>
+      <c r="F52">
+        <v>11.53</v>
+      </c>
+      <c r="G52">
+        <v>4.84</v>
+      </c>
+      <c r="H52">
+        <v>21.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.65</v>
+      </c>
+      <c r="K52">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L52">
+        <v>1.48</v>
+      </c>
+      <c r="M52">
+        <v>2.465114</v>
+      </c>
+      <c r="N52">
+        <v>-0.9851139999999998</v>
+      </c>
+      <c r="O52">
+        <v>-0.1970227999999999</v>
+      </c>
+      <c r="P52">
+        <v>-0.7880911999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-0.6180912</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1367271435510007</v>
+      </c>
+      <c r="T52">
+        <v>1.409263531058738</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1200755827113878</v>
+      </c>
+      <c r="W52">
+        <v>0.1881278404163053</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.6003779135569389</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.164177491983653</v>
+      </c>
+      <c r="C53">
+        <v>0.9448541104710166</v>
+      </c>
+      <c r="D53">
+        <v>7.865454110471016</v>
+      </c>
+      <c r="E53">
+        <v>9.900600000000001</v>
+      </c>
+      <c r="F53">
+        <v>11.7606</v>
+      </c>
+      <c r="G53">
+        <v>4.84</v>
+      </c>
+      <c r="H53">
+        <v>21.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.65</v>
+      </c>
+      <c r="K53">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L53">
+        <v>1.48</v>
+      </c>
+      <c r="M53">
+        <v>2.51441628</v>
+      </c>
+      <c r="N53">
+        <v>-1.03441628</v>
+      </c>
+      <c r="O53">
+        <v>-0.2068832559999999</v>
+      </c>
+      <c r="P53">
+        <v>-0.827533024</v>
+      </c>
+      <c r="Q53">
+        <v>-0.657533024</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1387256566846946</v>
+      </c>
+      <c r="T53">
+        <v>1.438024011284426</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.1177211595209684</v>
+      </c>
+      <c r="W53">
+        <v>0.1886312160944169</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5886057976048422</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.165927491983653</v>
+      </c>
+      <c r="C54">
+        <v>0.6088705515540127</v>
+      </c>
+      <c r="D54">
+        <v>7.760070551554013</v>
+      </c>
+      <c r="E54">
+        <v>10.1312</v>
+      </c>
+      <c r="F54">
+        <v>11.9912</v>
+      </c>
+      <c r="G54">
+        <v>4.84</v>
+      </c>
+      <c r="H54">
+        <v>21.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.65</v>
+      </c>
+      <c r="K54">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L54">
+        <v>1.48</v>
+      </c>
+      <c r="M54">
+        <v>2.56371856</v>
+      </c>
+      <c r="N54">
+        <v>-1.08371856</v>
+      </c>
+      <c r="O54">
+        <v>-0.2167437119999999</v>
+      </c>
+      <c r="P54">
+        <v>-0.8669748479999999</v>
+      </c>
+      <c r="Q54">
+        <v>-0.696974848</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1408074411989591</v>
+      </c>
+      <c r="T54">
+        <v>1.467982844852852</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.1154572910686421</v>
+      </c>
+      <c r="W54">
+        <v>0.1891152311695243</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5772864553432105</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.167677491983653</v>
+      </c>
+      <c r="C55">
+        <v>0.2756735741609742</v>
+      </c>
+      <c r="D55">
+        <v>7.657473574160974</v>
+      </c>
+      <c r="E55">
+        <v>10.3618</v>
+      </c>
+      <c r="F55">
+        <v>12.2218</v>
+      </c>
+      <c r="G55">
+        <v>4.84</v>
+      </c>
+      <c r="H55">
+        <v>21.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.65</v>
+      </c>
+      <c r="K55">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L55">
+        <v>1.48</v>
+      </c>
+      <c r="M55">
+        <v>2.61302084</v>
+      </c>
+      <c r="N55">
+        <v>-1.13302084</v>
+      </c>
+      <c r="O55">
+        <v>-0.2266041679999999</v>
+      </c>
+      <c r="P55">
+        <v>-0.906416672</v>
+      </c>
+      <c r="Q55">
+        <v>-0.736416672</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1429778122882987</v>
+      </c>
+      <c r="T55">
+        <v>1.499216522402913</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.1132788516145168</v>
+      </c>
+      <c r="W55">
+        <v>0.1895809815248163</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.5663942580725839</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.169427491983653</v>
+      </c>
+      <c r="C56">
+        <v>-0.05484590485599128</v>
+      </c>
+      <c r="D56">
+        <v>7.55755409514401</v>
+      </c>
+      <c r="E56">
+        <v>10.5924</v>
+      </c>
+      <c r="F56">
+        <v>12.4524</v>
+      </c>
+      <c r="G56">
+        <v>4.84</v>
+      </c>
+      <c r="H56">
+        <v>21.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.65</v>
+      </c>
+      <c r="K56">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L56">
+        <v>1.48</v>
+      </c>
+      <c r="M56">
+        <v>2.66232312</v>
+      </c>
+      <c r="N56">
+        <v>-1.18232312</v>
+      </c>
+      <c r="O56">
+        <v>-0.2364646239999999</v>
+      </c>
+      <c r="P56">
+        <v>-0.945858496</v>
+      </c>
+      <c r="Q56">
+        <v>-0.7758584960000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1452425473380443</v>
+      </c>
+      <c r="T56">
+        <v>1.531808185933411</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.1111810951031368</v>
+      </c>
+      <c r="W56">
+        <v>0.1900294818669493</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5559054755156843</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.171177491983653</v>
+      </c>
+      <c r="C57">
+        <v>-0.3827913484415717</v>
+      </c>
+      <c r="D57">
+        <v>7.460208651558429</v>
+      </c>
+      <c r="E57">
+        <v>10.823</v>
+      </c>
+      <c r="F57">
+        <v>12.683</v>
+      </c>
+      <c r="G57">
+        <v>4.84</v>
+      </c>
+      <c r="H57">
+        <v>21.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.65</v>
+      </c>
+      <c r="K57">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L57">
+        <v>1.48</v>
+      </c>
+      <c r="M57">
+        <v>2.7116254</v>
+      </c>
+      <c r="N57">
+        <v>-1.2316254</v>
+      </c>
+      <c r="O57">
+        <v>-0.2463250799999999</v>
+      </c>
+      <c r="P57">
+        <v>-0.98530032</v>
+      </c>
+      <c r="Q57">
+        <v>-0.8153003200000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1476079372788897</v>
+      </c>
+      <c r="T57">
+        <v>1.565848367843042</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.1091596206467162</v>
+      </c>
+      <c r="W57">
+        <v>0.1904616731057321</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.5457981032335808</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.172927491983653</v>
+      </c>
+      <c r="C58">
+        <v>-0.7082609566908591</v>
+      </c>
+      <c r="D58">
+        <v>7.365339043309141</v>
+      </c>
+      <c r="E58">
+        <v>11.0536</v>
+      </c>
+      <c r="F58">
+        <v>12.9136</v>
+      </c>
+      <c r="G58">
+        <v>4.84</v>
+      </c>
+      <c r="H58">
+        <v>21.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.65</v>
+      </c>
+      <c r="K58">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L58">
+        <v>1.48</v>
+      </c>
+      <c r="M58">
+        <v>2.76092768</v>
+      </c>
+      <c r="N58">
+        <v>-1.28092768</v>
+      </c>
+      <c r="O58">
+        <v>-0.2561855359999999</v>
+      </c>
+      <c r="P58">
+        <v>-1.024742144</v>
+      </c>
+      <c r="Q58">
+        <v>-0.8547421440000003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.150080844944319</v>
+      </c>
+      <c r="T58">
+        <v>1.601435830748566</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.1072103417065962</v>
+      </c>
+      <c r="W58">
+        <v>0.1908784289431297</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.5360517085329812</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.174677491983653</v>
+      </c>
+      <c r="C59">
+        <v>-1.03134799727907</v>
+      </c>
+      <c r="D59">
+        <v>7.27285200272093</v>
+      </c>
+      <c r="E59">
+        <v>11.2842</v>
+      </c>
+      <c r="F59">
+        <v>13.1442</v>
+      </c>
+      <c r="G59">
+        <v>4.84</v>
+      </c>
+      <c r="H59">
+        <v>21.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.65</v>
+      </c>
+      <c r="K59">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L59">
+        <v>1.48</v>
+      </c>
+      <c r="M59">
+        <v>2.81022996</v>
+      </c>
+      <c r="N59">
+        <v>-1.33022996</v>
+      </c>
+      <c r="O59">
+        <v>-0.266045992</v>
+      </c>
+      <c r="P59">
+        <v>-1.064183968</v>
+      </c>
+      <c r="Q59">
+        <v>-0.8941839680000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1526687715709311</v>
+      </c>
+      <c r="T59">
+        <v>1.638678524486905</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.1053294585187612</v>
+      </c>
+      <c r="W59">
+        <v>0.1912805617686889</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5266472925938062</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.176427491983653</v>
+      </c>
+      <c r="C60">
+        <v>-1.35214111130462</v>
+      </c>
+      <c r="D60">
+        <v>7.182658888695379</v>
+      </c>
+      <c r="E60">
+        <v>11.5148</v>
+      </c>
+      <c r="F60">
+        <v>13.3748</v>
+      </c>
+      <c r="G60">
+        <v>4.84</v>
+      </c>
+      <c r="H60">
+        <v>21.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.65</v>
+      </c>
+      <c r="K60">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L60">
+        <v>1.48</v>
+      </c>
+      <c r="M60">
+        <v>2.85953224</v>
+      </c>
+      <c r="N60">
+        <v>-1.37953224</v>
+      </c>
+      <c r="O60">
+        <v>-0.2759064479999999</v>
+      </c>
+      <c r="P60">
+        <v>-1.103625792</v>
+      </c>
+      <c r="Q60">
+        <v>-0.933625792</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1553799327988104</v>
+      </c>
+      <c r="T60">
+        <v>1.677694679831831</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.103513433371886</v>
+      </c>
+      <c r="W60">
+        <v>0.1916688279450908</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5175671668594302</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.178177491983653</v>
+      </c>
+      <c r="C61">
+        <v>-1.670724596653818</v>
+      </c>
+      <c r="D61">
+        <v>7.09467540334618</v>
+      </c>
+      <c r="E61">
+        <v>11.7454</v>
+      </c>
+      <c r="F61">
+        <v>13.6054</v>
+      </c>
+      <c r="G61">
+        <v>4.84</v>
+      </c>
+      <c r="H61">
+        <v>21.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.65</v>
+      </c>
+      <c r="K61">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L61">
+        <v>1.48</v>
+      </c>
+      <c r="M61">
+        <v>2.908834519999999</v>
+      </c>
+      <c r="N61">
+        <v>-1.428834519999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.2857669039999998</v>
+      </c>
+      <c r="P61">
+        <v>-1.143067616</v>
+      </c>
+      <c r="Q61">
+        <v>-0.9730676159999996</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1582233457939033</v>
+      </c>
+      <c r="T61">
+        <v>1.718614062266753</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.1017589683994812</v>
+      </c>
+      <c r="W61">
+        <v>0.1920439325561909</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.508794841997406</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.179927491983653</v>
+      </c>
+      <c r="C62">
+        <v>-1.987178670791202</v>
+      </c>
+      <c r="D62">
+        <v>7.008821329208796</v>
+      </c>
+      <c r="E62">
+        <v>11.976</v>
+      </c>
+      <c r="F62">
+        <v>13.836</v>
+      </c>
+      <c r="G62">
+        <v>4.84</v>
+      </c>
+      <c r="H62">
+        <v>21.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.65</v>
+      </c>
+      <c r="K62">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L62">
+        <v>1.48</v>
+      </c>
+      <c r="M62">
+        <v>2.9581368</v>
+      </c>
+      <c r="N62">
+        <v>-1.4781368</v>
+      </c>
+      <c r="O62">
+        <v>-0.2956273599999999</v>
+      </c>
+      <c r="P62">
+        <v>-1.18250944</v>
+      </c>
+      <c r="Q62">
+        <v>-1.01250944</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1612089294387509</v>
+      </c>
+      <c r="T62">
+        <v>1.761579413823422</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.1000629855928231</v>
+      </c>
+      <c r="W62">
+        <v>0.1924065336802544</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.5003149279641159</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1972549028518297</v>
+      </c>
+      <c r="C63">
+        <v>-2.967709730713812</v>
+      </c>
+      <c r="D63">
+        <v>6.258890269286187</v>
+      </c>
+      <c r="E63">
+        <v>12.2066</v>
+      </c>
+      <c r="F63">
+        <v>14.0666</v>
+      </c>
+      <c r="G63">
+        <v>4.84</v>
+      </c>
+      <c r="H63">
+        <v>21.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.65</v>
+      </c>
+      <c r="K63">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L63">
+        <v>1.48</v>
+      </c>
+      <c r="M63">
+        <v>3.35910408</v>
+      </c>
+      <c r="N63">
+        <v>-1.87910408</v>
+      </c>
+      <c r="O63">
+        <v>-0.3758208159999999</v>
+      </c>
+      <c r="P63">
+        <v>-1.503283264</v>
+      </c>
+      <c r="Q63">
+        <v>-1.333283264</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1651871349837873</v>
+      </c>
+      <c r="T63">
+        <v>1.818829526411007</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08811873432632666</v>
+      </c>
+      <c r="W63">
+        <v>0.2177572462428732</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4405936716316334</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1992549028518297</v>
+      </c>
+      <c r="C64">
+        <v>-3.274665042517965</v>
+      </c>
+      <c r="D64">
+        <v>6.182534957482035</v>
+      </c>
+      <c r="E64">
+        <v>12.4372</v>
+      </c>
+      <c r="F64">
+        <v>14.2972</v>
+      </c>
+      <c r="G64">
+        <v>4.84</v>
+      </c>
+      <c r="H64">
+        <v>21.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.65</v>
+      </c>
+      <c r="K64">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L64">
+        <v>1.48</v>
+      </c>
+      <c r="M64">
+        <v>3.41417136</v>
+      </c>
+      <c r="N64">
+        <v>-1.93417136</v>
+      </c>
+      <c r="O64">
+        <v>-0.3868342719999999</v>
+      </c>
+      <c r="P64">
+        <v>-1.547337088</v>
+      </c>
+      <c r="Q64">
+        <v>-1.377337088</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1685131122202027</v>
+      </c>
+      <c r="T64">
+        <v>1.86669346131656</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08669746441783753</v>
+      </c>
+      <c r="W64">
+        <v>0.2180966454970204</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4334873220891877</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2012549028518297</v>
+      </c>
+      <c r="C65">
+        <v>-3.579779815209285</v>
+      </c>
+      <c r="D65">
+        <v>6.108020184790715</v>
+      </c>
+      <c r="E65">
+        <v>12.6678</v>
+      </c>
+      <c r="F65">
+        <v>14.5278</v>
+      </c>
+      <c r="G65">
+        <v>4.84</v>
+      </c>
+      <c r="H65">
+        <v>21.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.65</v>
+      </c>
+      <c r="K65">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L65">
+        <v>1.48</v>
+      </c>
+      <c r="M65">
+        <v>3.46923864</v>
+      </c>
+      <c r="N65">
+        <v>-1.98923864</v>
+      </c>
+      <c r="O65">
+        <v>-0.3978477279999999</v>
+      </c>
+      <c r="P65">
+        <v>-1.591390912</v>
+      </c>
+      <c r="Q65">
+        <v>-1.421390912</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.172018872009938</v>
+      </c>
+      <c r="T65">
+        <v>1.917144635946737</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08532131418898296</v>
+      </c>
+      <c r="W65">
+        <v>0.2184252701716709</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4266065709449148</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2032549028518297</v>
+      </c>
+      <c r="C66">
+        <v>-3.883119805346947</v>
+      </c>
+      <c r="D66">
+        <v>6.035280194653053</v>
+      </c>
+      <c r="E66">
+        <v>12.8984</v>
+      </c>
+      <c r="F66">
+        <v>14.7584</v>
+      </c>
+      <c r="G66">
+        <v>4.84</v>
+      </c>
+      <c r="H66">
+        <v>21.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.65</v>
+      </c>
+      <c r="K66">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L66">
+        <v>1.48</v>
+      </c>
+      <c r="M66">
+        <v>3.52430592</v>
+      </c>
+      <c r="N66">
+        <v>-2.04430592</v>
+      </c>
+      <c r="O66">
+        <v>-0.4088611839999999</v>
+      </c>
+      <c r="P66">
+        <v>-1.635444736</v>
+      </c>
+      <c r="Q66">
+        <v>-1.465444736</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1757193962324362</v>
+      </c>
+      <c r="T66">
+        <v>1.970398653611924</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08398816865478009</v>
+      </c>
+      <c r="W66">
+        <v>0.2187436253252385</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4199408432739006</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2052549028518297</v>
+      </c>
+      <c r="C67">
+        <v>-4.18474767399292</v>
+      </c>
+      <c r="D67">
+        <v>5.964252326007079</v>
+      </c>
+      <c r="E67">
+        <v>13.129</v>
+      </c>
+      <c r="F67">
+        <v>14.989</v>
+      </c>
+      <c r="G67">
+        <v>4.84</v>
+      </c>
+      <c r="H67">
+        <v>21.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.65</v>
+      </c>
+      <c r="K67">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L67">
+        <v>1.48</v>
+      </c>
+      <c r="M67">
+        <v>3.5793732</v>
+      </c>
+      <c r="N67">
+        <v>-2.0993732</v>
+      </c>
+      <c r="O67">
+        <v>-0.4198746399999999</v>
+      </c>
+      <c r="P67">
+        <v>-1.67949856</v>
+      </c>
+      <c r="Q67">
+        <v>-1.50949856</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1796313789819344</v>
+      </c>
+      <c r="T67">
+        <v>2.026695758000836</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0826960429831681</v>
+      </c>
+      <c r="W67">
+        <v>0.2190521849356195</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4134802149158405</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2072549028518297</v>
+      </c>
+      <c r="C68">
+        <v>-4.484723166744299</v>
+      </c>
+      <c r="D68">
+        <v>5.894876833255702</v>
+      </c>
+      <c r="E68">
+        <v>13.3596</v>
+      </c>
+      <c r="F68">
+        <v>15.2196</v>
+      </c>
+      <c r="G68">
+        <v>4.84</v>
+      </c>
+      <c r="H68">
+        <v>21.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.65</v>
+      </c>
+      <c r="K68">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L68">
+        <v>1.48</v>
+      </c>
+      <c r="M68">
+        <v>3.63444048</v>
+      </c>
+      <c r="N68">
+        <v>-2.15444048</v>
+      </c>
+      <c r="O68">
+        <v>-0.4308880959999999</v>
+      </c>
+      <c r="P68">
+        <v>-1.723552384</v>
+      </c>
+      <c r="Q68">
+        <v>-1.553552384000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.183773478363756</v>
+      </c>
+      <c r="T68">
+        <v>2.086304456765567</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.08144307263493826</v>
+      </c>
+      <c r="W68">
+        <v>0.2193513942547768</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.4072153631746914</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2092549028518297</v>
+      </c>
+      <c r="C69">
+        <v>-4.783103281345392</v>
+      </c>
+      <c r="D69">
+        <v>5.827096718654608</v>
+      </c>
+      <c r="E69">
+        <v>13.5902</v>
+      </c>
+      <c r="F69">
+        <v>15.4502</v>
+      </c>
+      <c r="G69">
+        <v>4.84</v>
+      </c>
+      <c r="H69">
+        <v>21.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.65</v>
+      </c>
+      <c r="K69">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L69">
+        <v>1.48</v>
+      </c>
+      <c r="M69">
+        <v>3.68950776</v>
+      </c>
+      <c r="N69">
+        <v>-2.20950776</v>
+      </c>
+      <c r="O69">
+        <v>-0.4419015519999999</v>
+      </c>
+      <c r="P69">
+        <v>-1.767606208</v>
+      </c>
+      <c r="Q69">
+        <v>-1.597606208</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1881666140717486</v>
+      </c>
+      <c r="T69">
+        <v>2.149525803940281</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08022750438665562</v>
+      </c>
+      <c r="W69">
+        <v>0.2196416719524666</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.4011375219332781</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2112549028518297</v>
+      </c>
+      <c r="C70">
+        <v>-5.079942423867925</v>
+      </c>
+      <c r="D70">
+        <v>5.760857576132074</v>
+      </c>
+      <c r="E70">
+        <v>13.8208</v>
+      </c>
+      <c r="F70">
+        <v>15.6808</v>
+      </c>
+      <c r="G70">
+        <v>4.84</v>
+      </c>
+      <c r="H70">
+        <v>21.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.65</v>
+      </c>
+      <c r="K70">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L70">
+        <v>1.48</v>
+      </c>
+      <c r="M70">
+        <v>3.74457504</v>
+      </c>
+      <c r="N70">
+        <v>-2.26457504</v>
+      </c>
+      <c r="O70">
+        <v>-0.4529150079999999</v>
+      </c>
+      <c r="P70">
+        <v>-1.811660032</v>
+      </c>
+      <c r="Q70">
+        <v>-1.641660032</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1928343207614908</v>
+      </c>
+      <c r="T70">
+        <v>2.216698485313415</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07904768814567538</v>
+      </c>
+      <c r="W70">
+        <v>0.2199234120708127</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.395238440728377</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2132549028518297</v>
+      </c>
+      <c r="C71">
+        <v>-5.375292554358744</v>
+      </c>
+      <c r="D71">
+        <v>5.696107445641257</v>
+      </c>
+      <c r="E71">
+        <v>14.0514</v>
+      </c>
+      <c r="F71">
+        <v>15.9114</v>
+      </c>
+      <c r="G71">
+        <v>4.84</v>
+      </c>
+      <c r="H71">
+        <v>21.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.65</v>
+      </c>
+      <c r="K71">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L71">
+        <v>1.48</v>
+      </c>
+      <c r="M71">
+        <v>3.79964232</v>
+      </c>
+      <c r="N71">
+        <v>-2.31964232</v>
+      </c>
+      <c r="O71">
+        <v>-0.4639284639999999</v>
+      </c>
+      <c r="P71">
+        <v>-1.855713856</v>
+      </c>
+      <c r="Q71">
+        <v>-1.685713856</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1978031698183131</v>
+      </c>
+      <c r="T71">
+        <v>2.288204888065461</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07790206947689748</v>
+      </c>
+      <c r="W71">
+        <v>0.2201969858089169</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3895103473844874</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2152549028518297</v>
+      </c>
+      <c r="C72">
+        <v>-5.669203322774489</v>
+      </c>
+      <c r="D72">
+        <v>5.632796677225509</v>
+      </c>
+      <c r="E72">
+        <v>14.282</v>
+      </c>
+      <c r="F72">
+        <v>16.142</v>
+      </c>
+      <c r="G72">
+        <v>4.84</v>
+      </c>
+      <c r="H72">
+        <v>21.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.65</v>
+      </c>
+      <c r="K72">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L72">
+        <v>1.48</v>
+      </c>
+      <c r="M72">
+        <v>3.8547096</v>
+      </c>
+      <c r="N72">
+        <v>-2.3747096</v>
+      </c>
+      <c r="O72">
+        <v>-0.4749419199999999</v>
+      </c>
+      <c r="P72">
+        <v>-1.89976768</v>
+      </c>
+      <c r="Q72">
+        <v>-1.72976768</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2031032754789235</v>
+      </c>
+      <c r="T72">
+        <v>2.36447838433431</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07678918277008466</v>
+      </c>
+      <c r="W72">
+        <v>0.2204627431545038</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3839459138504234</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2172549028518297</v>
+      </c>
+      <c r="C73">
+        <v>-5.961722195950674</v>
+      </c>
+      <c r="D73">
+        <v>5.570877804049325</v>
+      </c>
+      <c r="E73">
+        <v>14.5126</v>
+      </c>
+      <c r="F73">
+        <v>16.3726</v>
+      </c>
+      <c r="G73">
+        <v>4.84</v>
+      </c>
+      <c r="H73">
+        <v>21.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.65</v>
+      </c>
+      <c r="K73">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L73">
+        <v>1.48</v>
+      </c>
+      <c r="M73">
+        <v>3.90977688</v>
+      </c>
+      <c r="N73">
+        <v>-2.42977688</v>
+      </c>
+      <c r="O73">
+        <v>-0.4859553759999999</v>
+      </c>
+      <c r="P73">
+        <v>-1.943821504</v>
+      </c>
+      <c r="Q73">
+        <v>-1.773821504</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2087689056678519</v>
+      </c>
+      <c r="T73">
+        <v>2.446012121725147</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07570764498459051</v>
+      </c>
+      <c r="W73">
+        <v>0.2207210143776798</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3785382249229526</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2192549028518297</v>
+      </c>
+      <c r="C74">
+        <v>-6.252894576287495</v>
+      </c>
+      <c r="D74">
+        <v>5.510305423712501</v>
+      </c>
+      <c r="E74">
+        <v>14.7432</v>
+      </c>
+      <c r="F74">
+        <v>16.6032</v>
+      </c>
+      <c r="G74">
+        <v>4.84</v>
+      </c>
+      <c r="H74">
+        <v>21.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.65</v>
+      </c>
+      <c r="K74">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L74">
+        <v>1.48</v>
+      </c>
+      <c r="M74">
+        <v>3.96484416</v>
+      </c>
+      <c r="N74">
+        <v>-2.48484416</v>
+      </c>
+      <c r="O74">
+        <v>-0.4969688319999999</v>
+      </c>
+      <c r="P74">
+        <v>-1.987875328</v>
+      </c>
+      <c r="Q74">
+        <v>-1.817875328</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.214839223727418</v>
+      </c>
+      <c r="T74">
+        <v>2.533369697501045</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07465614991536008</v>
+      </c>
+      <c r="W74">
+        <v>0.220972111400212</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3732807495768006</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2212549028518297</v>
+      </c>
+      <c r="C75">
+        <v>-6.542763912776101</v>
+      </c>
+      <c r="D75">
+        <v>5.451036087223899</v>
+      </c>
+      <c r="E75">
+        <v>14.9738</v>
+      </c>
+      <c r="F75">
+        <v>16.8338</v>
+      </c>
+      <c r="G75">
+        <v>4.84</v>
+      </c>
+      <c r="H75">
+        <v>21.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.65</v>
+      </c>
+      <c r="K75">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L75">
+        <v>1.48</v>
+      </c>
+      <c r="M75">
+        <v>4.01991144</v>
+      </c>
+      <c r="N75">
+        <v>-2.53991144</v>
+      </c>
+      <c r="O75">
+        <v>-0.507982288</v>
+      </c>
+      <c r="P75">
+        <v>-2.031929152</v>
+      </c>
+      <c r="Q75">
+        <v>-1.861929152000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2213591949765816</v>
+      </c>
+      <c r="T75">
+        <v>2.627198204815899</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07363346293021816</v>
+      </c>
+      <c r="W75">
+        <v>0.2212163290522639</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3681673146510909</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2232549028518297</v>
+      </c>
+      <c r="C76">
+        <v>-6.831371804935809</v>
+      </c>
+      <c r="D76">
+        <v>5.393028195064191</v>
+      </c>
+      <c r="E76">
+        <v>15.2044</v>
+      </c>
+      <c r="F76">
+        <v>17.0644</v>
+      </c>
+      <c r="G76">
+        <v>4.84</v>
+      </c>
+      <c r="H76">
+        <v>21.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.65</v>
+      </c>
+      <c r="K76">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L76">
+        <v>1.48</v>
+      </c>
+      <c r="M76">
+        <v>4.07497872</v>
+      </c>
+      <c r="N76">
+        <v>-2.59497872</v>
+      </c>
+      <c r="O76">
+        <v>-0.5189957439999998</v>
+      </c>
+      <c r="P76">
+        <v>-2.075982976</v>
+      </c>
+      <c r="Q76">
+        <v>-1.905982976</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2283807024756809</v>
+      </c>
+      <c r="T76">
+        <v>2.72824428961651</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07263841613386386</v>
+      </c>
+      <c r="W76">
+        <v>0.2214539462272333</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3631920806693194</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2252549028518297</v>
+      </c>
+      <c r="C77">
+        <v>-7.118758100184909</v>
+      </c>
+      <c r="D77">
+        <v>5.33624189981509</v>
+      </c>
+      <c r="E77">
+        <v>15.435</v>
+      </c>
+      <c r="F77">
+        <v>17.295</v>
+      </c>
+      <c r="G77">
+        <v>4.84</v>
+      </c>
+      <c r="H77">
+        <v>21.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.65</v>
+      </c>
+      <c r="K77">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L77">
+        <v>1.48</v>
+      </c>
+      <c r="M77">
+        <v>4.130046</v>
+      </c>
+      <c r="N77">
+        <v>-2.650046</v>
+      </c>
+      <c r="O77">
+        <v>-0.5300092</v>
+      </c>
+      <c r="P77">
+        <v>-2.1200368</v>
+      </c>
+      <c r="Q77">
+        <v>-1.9500368</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2359639305747082</v>
+      </c>
+      <c r="T77">
+        <v>2.837374061201171</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07166990391874567</v>
+      </c>
+      <c r="W77">
+        <v>0.2216852269442036</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3583495195937285</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2272549028518297</v>
+      </c>
+      <c r="C78">
+        <v>-7.404960985123861</v>
+      </c>
+      <c r="D78">
+        <v>5.280639014876141</v>
+      </c>
+      <c r="E78">
+        <v>15.6656</v>
+      </c>
+      <c r="F78">
+        <v>17.5256</v>
+      </c>
+      <c r="G78">
+        <v>4.84</v>
+      </c>
+      <c r="H78">
+        <v>21.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.65</v>
+      </c>
+      <c r="K78">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L78">
+        <v>1.48</v>
+      </c>
+      <c r="M78">
+        <v>4.18511328</v>
+      </c>
+      <c r="N78">
+        <v>-2.70511328</v>
+      </c>
+      <c r="O78">
+        <v>-0.541022656</v>
+      </c>
+      <c r="P78">
+        <v>-2.164090624</v>
+      </c>
+      <c r="Q78">
+        <v>-1.994090624</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2441790943486544</v>
+      </c>
+      <c r="T78">
+        <v>2.955597980417887</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07072687886718323</v>
+      </c>
+      <c r="W78">
+        <v>0.2219104213265167</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3536343943359163</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2292549028518297</v>
+      </c>
+      <c r="C79">
+        <v>-7.690017071170423</v>
+      </c>
+      <c r="D79">
+        <v>5.226182928829576</v>
+      </c>
+      <c r="E79">
+        <v>15.8962</v>
+      </c>
+      <c r="F79">
+        <v>17.7562</v>
+      </c>
+      <c r="G79">
+        <v>4.84</v>
+      </c>
+      <c r="H79">
+        <v>21.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.65</v>
+      </c>
+      <c r="K79">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L79">
+        <v>1.48</v>
+      </c>
+      <c r="M79">
+        <v>4.24018056</v>
+      </c>
+      <c r="N79">
+        <v>-2.76018056</v>
+      </c>
+      <c r="O79">
+        <v>-0.5520361119999998</v>
+      </c>
+      <c r="P79">
+        <v>-2.208144448</v>
+      </c>
+      <c r="Q79">
+        <v>-2.038144448</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2531086201899002</v>
+      </c>
+      <c r="T79">
+        <v>3.084102240436056</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06980834797280423</v>
+      </c>
+      <c r="W79">
+        <v>0.2221297665040944</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3490417398640213</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2312549028518297</v>
+      </c>
+      <c r="C80">
+        <v>-7.973961474950258</v>
+      </c>
+      <c r="D80">
+        <v>5.17283852504974</v>
+      </c>
+      <c r="E80">
+        <v>16.1268</v>
+      </c>
+      <c r="F80">
+        <v>17.9868</v>
+      </c>
+      <c r="G80">
+        <v>4.84</v>
+      </c>
+      <c r="H80">
+        <v>21.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.65</v>
+      </c>
+      <c r="K80">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L80">
+        <v>1.48</v>
+      </c>
+      <c r="M80">
+        <v>4.29524784</v>
+      </c>
+      <c r="N80">
+        <v>-2.81524784</v>
+      </c>
+      <c r="O80">
+        <v>-0.5630495679999998</v>
+      </c>
+      <c r="P80">
+        <v>-2.252198272</v>
+      </c>
+      <c r="Q80">
+        <v>-2.082198272</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.262849921107623</v>
+      </c>
+      <c r="T80">
+        <v>3.224288705910422</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06891336915264007</v>
+      </c>
+      <c r="W80">
+        <v>0.2223434874463496</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3445668457632005</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2332549028518297</v>
+      </c>
+      <c r="C81">
+        <v>-8.256827893813888</v>
+      </c>
+      <c r="D81">
+        <v>5.120572106186112</v>
+      </c>
+      <c r="E81">
+        <v>16.3574</v>
+      </c>
+      <c r="F81">
+        <v>18.2174</v>
+      </c>
+      <c r="G81">
+        <v>4.84</v>
+      </c>
+      <c r="H81">
+        <v>21.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.65</v>
+      </c>
+      <c r="K81">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L81">
+        <v>1.48</v>
+      </c>
+      <c r="M81">
+        <v>4.35031512</v>
+      </c>
+      <c r="N81">
+        <v>-2.87031512</v>
+      </c>
+      <c r="O81">
+        <v>-0.574063024</v>
+      </c>
+      <c r="P81">
+        <v>-2.296252096</v>
+      </c>
+      <c r="Q81">
+        <v>-2.126252096</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2735189649698908</v>
+      </c>
+      <c r="T81">
+        <v>3.377826263334728</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06804104802412565</v>
+      </c>
+      <c r="W81">
+        <v>0.2225517977318388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3402052401206282</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2352549028518297</v>
+      </c>
+      <c r="C82">
+        <v>-8.538648676821335</v>
+      </c>
+      <c r="D82">
+        <v>5.069351323178665</v>
+      </c>
+      <c r="E82">
+        <v>16.588</v>
+      </c>
+      <c r="F82">
+        <v>18.448</v>
+      </c>
+      <c r="G82">
+        <v>4.84</v>
+      </c>
+      <c r="H82">
+        <v>21.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.65</v>
+      </c>
+      <c r="K82">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L82">
+        <v>1.48</v>
+      </c>
+      <c r="M82">
+        <v>4.405382400000001</v>
+      </c>
+      <c r="N82">
+        <v>-2.925382400000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.58507648</v>
+      </c>
+      <c r="P82">
+        <v>-2.34030592</v>
+      </c>
+      <c r="Q82">
+        <v>-2.170305920000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2852549132183853</v>
+      </c>
+      <c r="T82">
+        <v>3.546717576501464</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06719053492382407</v>
+      </c>
+      <c r="W82">
+        <v>0.2227549002601908</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3359526746191204</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2372549028518297</v>
+      </c>
+      <c r="C83">
+        <v>-8.819454891508624</v>
+      </c>
+      <c r="D83">
+        <v>5.019145108491375</v>
+      </c>
+      <c r="E83">
+        <v>16.8186</v>
+      </c>
+      <c r="F83">
+        <v>18.6786</v>
+      </c>
+      <c r="G83">
+        <v>4.84</v>
+      </c>
+      <c r="H83">
+        <v>21.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.65</v>
+      </c>
+      <c r="K83">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L83">
+        <v>1.48</v>
+      </c>
+      <c r="M83">
+        <v>4.46044968</v>
+      </c>
+      <c r="N83">
+        <v>-2.98044968</v>
+      </c>
+      <c r="O83">
+        <v>-0.5960899359999998</v>
+      </c>
+      <c r="P83">
+        <v>-2.384359744</v>
+      </c>
+      <c r="Q83">
+        <v>-2.214359744</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2982262244404056</v>
+      </c>
+      <c r="T83">
+        <v>3.733386922633121</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06636102214698675</v>
+      </c>
+      <c r="W83">
+        <v>0.2229529879112996</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3318051107349338</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2392549028518297</v>
+      </c>
+      <c r="C84">
+        <v>-9.099276386725698</v>
+      </c>
+      <c r="D84">
+        <v>4.969923613274304</v>
+      </c>
+      <c r="E84">
+        <v>17.0492</v>
+      </c>
+      <c r="F84">
+        <v>18.9092</v>
+      </c>
+      <c r="G84">
+        <v>4.84</v>
+      </c>
+      <c r="H84">
+        <v>21.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.65</v>
+      </c>
+      <c r="K84">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L84">
+        <v>1.48</v>
+      </c>
+      <c r="M84">
+        <v>4.515516960000001</v>
+      </c>
+      <c r="N84">
+        <v>-3.035516960000001</v>
+      </c>
+      <c r="O84">
+        <v>-0.6071033920000001</v>
+      </c>
+      <c r="P84">
+        <v>-2.428413568000001</v>
+      </c>
+      <c r="Q84">
+        <v>-2.258413568000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3126387924648725</v>
+      </c>
+      <c r="T84">
+        <v>3.94079730722385</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06555174138909665</v>
+      </c>
+      <c r="W84">
+        <v>0.2231462441562837</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.3277587069454833</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2412549028518297</v>
+      </c>
+      <c r="C85">
+        <v>-9.37814185181281</v>
+      </c>
+      <c r="D85">
+        <v>4.921658148187191</v>
+      </c>
+      <c r="E85">
+        <v>17.2798</v>
+      </c>
+      <c r="F85">
+        <v>19.1398</v>
+      </c>
+      <c r="G85">
+        <v>4.84</v>
+      </c>
+      <c r="H85">
+        <v>21.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.65</v>
+      </c>
+      <c r="K85">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L85">
+        <v>1.48</v>
+      </c>
+      <c r="M85">
+        <v>4.570584240000001</v>
+      </c>
+      <c r="N85">
+        <v>-3.090584240000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.618116848</v>
+      </c>
+      <c r="P85">
+        <v>-2.472467392</v>
+      </c>
+      <c r="Q85">
+        <v>-2.302467392000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3287469567275121</v>
+      </c>
+      <c r="T85">
+        <v>4.172608913531135</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06476196137236055</v>
+      </c>
+      <c r="W85">
+        <v>0.2233348436242803</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3238098068618028</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2432549028518297</v>
+      </c>
+      <c r="C86">
+        <v>-9.656078872361981</v>
+      </c>
+      <c r="D86">
+        <v>4.874321127638017</v>
+      </c>
+      <c r="E86">
+        <v>17.5104</v>
+      </c>
+      <c r="F86">
+        <v>19.3704</v>
+      </c>
+      <c r="G86">
+        <v>4.84</v>
+      </c>
+      <c r="H86">
+        <v>21.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.65</v>
+      </c>
+      <c r="K86">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L86">
+        <v>1.48</v>
+      </c>
+      <c r="M86">
+        <v>4.625651519999999</v>
+      </c>
+      <c r="N86">
+        <v>-3.145651519999999</v>
+      </c>
+      <c r="O86">
+        <v>-0.6291303039999997</v>
+      </c>
+      <c r="P86">
+        <v>-2.516521215999999</v>
+      </c>
+      <c r="Q86">
+        <v>-2.346521215999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3468686415229815</v>
+      </c>
+      <c r="T86">
+        <v>4.43339697062683</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06399098564173723</v>
+      </c>
+      <c r="W86">
+        <v>0.2235189526287532</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3199549282086862</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2452549028518297</v>
+      </c>
+      <c r="C87">
+        <v>-9.933113982791152</v>
+      </c>
+      <c r="D87">
+        <v>4.827886017208848</v>
+      </c>
+      <c r="E87">
+        <v>17.741</v>
+      </c>
+      <c r="F87">
+        <v>19.601</v>
+      </c>
+      <c r="G87">
+        <v>4.84</v>
+      </c>
+      <c r="H87">
+        <v>21.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.65</v>
+      </c>
+      <c r="K87">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L87">
+        <v>1.48</v>
+      </c>
+      <c r="M87">
+        <v>4.6807188</v>
+      </c>
+      <c r="N87">
+        <v>-3.2007188</v>
+      </c>
+      <c r="O87">
+        <v>-0.64014376</v>
+      </c>
+      <c r="P87">
+        <v>-2.56057504</v>
+      </c>
+      <c r="Q87">
+        <v>-2.39057504</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.367406550957847</v>
+      </c>
+      <c r="T87">
+        <v>4.728956768668619</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0632381505165403</v>
+      </c>
+      <c r="W87">
+        <v>0.2236987296566502</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3161907525827016</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2472549028518297</v>
+      </c>
+      <c r="C88">
+        <v>-10.2092727159416</v>
+      </c>
+      <c r="D88">
+        <v>4.782327284058395</v>
+      </c>
+      <c r="E88">
+        <v>17.9716</v>
+      </c>
+      <c r="F88">
+        <v>19.8316</v>
+      </c>
+      <c r="G88">
+        <v>4.84</v>
+      </c>
+      <c r="H88">
+        <v>21.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.65</v>
+      </c>
+      <c r="K88">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L88">
+        <v>1.48</v>
+      </c>
+      <c r="M88">
+        <v>4.73578608</v>
+      </c>
+      <c r="N88">
+        <v>-3.25578608</v>
+      </c>
+      <c r="O88">
+        <v>-0.6511572159999998</v>
+      </c>
+      <c r="P88">
+        <v>-2.604628864</v>
+      </c>
+      <c r="Q88">
+        <v>-2.434628864</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.390878447454836</v>
+      </c>
+      <c r="T88">
+        <v>5.066739395002092</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06250282318495264</v>
+      </c>
+      <c r="W88">
+        <v>0.2238743258234333</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3125141159247633</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2492549028518297</v>
+      </c>
+      <c r="C89">
+        <v>-10.4845796498935</v>
+      </c>
+      <c r="D89">
+        <v>4.737620350106496</v>
+      </c>
+      <c r="E89">
+        <v>18.2022</v>
+      </c>
+      <c r="F89">
+        <v>20.0622</v>
+      </c>
+      <c r="G89">
+        <v>4.84</v>
+      </c>
+      <c r="H89">
+        <v>21.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.65</v>
+      </c>
+      <c r="K89">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L89">
+        <v>1.48</v>
+      </c>
+      <c r="M89">
+        <v>4.79085336</v>
+      </c>
+      <c r="N89">
+        <v>-3.31085336</v>
+      </c>
+      <c r="O89">
+        <v>-0.6621706719999998</v>
+      </c>
+      <c r="P89">
+        <v>-2.648682688</v>
+      </c>
+      <c r="Q89">
+        <v>-2.478682688</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4179614049513619</v>
+      </c>
+      <c r="T89">
+        <v>5.456488579233021</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06178439992995318</v>
+      </c>
+      <c r="W89">
+        <v>0.2240458852967272</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.308921999649766</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2512549028518297</v>
+      </c>
+      <c r="C90">
+        <v>-10.75905845217983</v>
+      </c>
+      <c r="D90">
+        <v>4.693741547820172</v>
+      </c>
+      <c r="E90">
+        <v>18.4328</v>
+      </c>
+      <c r="F90">
+        <v>20.2928</v>
+      </c>
+      <c r="G90">
+        <v>4.84</v>
+      </c>
+      <c r="H90">
+        <v>21.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.65</v>
+      </c>
+      <c r="K90">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L90">
+        <v>1.48</v>
+      </c>
+      <c r="M90">
+        <v>4.84592064</v>
+      </c>
+      <c r="N90">
+        <v>-3.36592064</v>
+      </c>
+      <c r="O90">
+        <v>-0.6731841279999998</v>
+      </c>
+      <c r="P90">
+        <v>-2.692736512</v>
+      </c>
+      <c r="Q90">
+        <v>-2.522736512</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4495581886973087</v>
+      </c>
+      <c r="T90">
+        <v>5.911195960835774</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06108230447620371</v>
+      </c>
+      <c r="W90">
+        <v>0.2242135456910826</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3054115223810185</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2532549028518297</v>
+      </c>
+      <c r="C91">
+        <v>-11.03273192156585</v>
+      </c>
+      <c r="D91">
+        <v>4.650668078434147</v>
+      </c>
+      <c r="E91">
+        <v>18.6634</v>
+      </c>
+      <c r="F91">
+        <v>20.5234</v>
+      </c>
+      <c r="G91">
+        <v>4.84</v>
+      </c>
+      <c r="H91">
+        <v>21.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.65</v>
+      </c>
+      <c r="K91">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L91">
+        <v>1.48</v>
+      </c>
+      <c r="M91">
+        <v>4.90098792</v>
+      </c>
+      <c r="N91">
+        <v>-3.42098792</v>
+      </c>
+      <c r="O91">
+        <v>-0.684197584</v>
+      </c>
+      <c r="P91">
+        <v>-2.736790336</v>
+      </c>
+      <c r="Q91">
+        <v>-2.566790336</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4868998422152459</v>
+      </c>
+      <c r="T91">
+        <v>6.448577411820844</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06039598644838119</v>
+      </c>
+      <c r="W91">
+        <v>0.2243774384361266</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.301979932241906</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2552549028518297</v>
+      </c>
+      <c r="C92">
+        <v>-11.30562202754917</v>
+      </c>
+      <c r="D92">
+        <v>4.608377972450833</v>
+      </c>
+      <c r="E92">
+        <v>18.894</v>
+      </c>
+      <c r="F92">
+        <v>20.754</v>
+      </c>
+      <c r="G92">
+        <v>4.84</v>
+      </c>
+      <c r="H92">
+        <v>21.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.65</v>
+      </c>
+      <c r="K92">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L92">
+        <v>1.48</v>
+      </c>
+      <c r="M92">
+        <v>4.9560552</v>
+      </c>
+      <c r="N92">
+        <v>-3.4760552</v>
+      </c>
+      <c r="O92">
+        <v>-0.6952110399999998</v>
+      </c>
+      <c r="P92">
+        <v>-2.78084416</v>
+      </c>
+      <c r="Q92">
+        <v>-2.61084416</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5317098264367706</v>
+      </c>
+      <c r="T92">
+        <v>7.093435153002929</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.05972491993228807</v>
+      </c>
+      <c r="W92">
+        <v>0.2245376891201696</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2986245996614404</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2572549028518297</v>
+      </c>
+      <c r="C93">
+        <v>-11.57774994772396</v>
+      </c>
+      <c r="D93">
+        <v>4.566850052276043</v>
+      </c>
+      <c r="E93">
+        <v>19.1246</v>
+      </c>
+      <c r="F93">
+        <v>20.9846</v>
+      </c>
+      <c r="G93">
+        <v>4.84</v>
+      </c>
+      <c r="H93">
+        <v>21.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.65</v>
+      </c>
+      <c r="K93">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L93">
+        <v>1.48</v>
+      </c>
+      <c r="M93">
+        <v>5.01112248</v>
+      </c>
+      <c r="N93">
+        <v>-3.53112248</v>
+      </c>
+      <c r="O93">
+        <v>-0.7062244959999998</v>
+      </c>
+      <c r="P93">
+        <v>-2.824897984</v>
+      </c>
+      <c r="Q93">
+        <v>-2.654897984</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5864775849297452</v>
+      </c>
+      <c r="T93">
+        <v>7.8815946144477</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05906860213083436</v>
+      </c>
+      <c r="W93">
+        <v>0.2246944178111568</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2953430106541718</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2592549028518297</v>
+      </c>
+      <c r="C94">
+        <v>-11.84913610314313</v>
+      </c>
+      <c r="D94">
+        <v>4.52606389685687</v>
+      </c>
+      <c r="E94">
+        <v>19.3552</v>
+      </c>
+      <c r="F94">
+        <v>21.2152</v>
+      </c>
+      <c r="G94">
+        <v>4.84</v>
+      </c>
+      <c r="H94">
+        <v>21.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.65</v>
+      </c>
+      <c r="K94">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L94">
+        <v>1.48</v>
+      </c>
+      <c r="M94">
+        <v>5.06618976</v>
+      </c>
+      <c r="N94">
+        <v>-3.58618976</v>
+      </c>
+      <c r="O94">
+        <v>-0.717237952</v>
+      </c>
+      <c r="P94">
+        <v>-2.868951808</v>
+      </c>
+      <c r="Q94">
+        <v>-2.698951808</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6549372830459634</v>
+      </c>
+      <c r="T94">
+        <v>8.866793941253665</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05842655210767311</v>
+      </c>
+      <c r="W94">
+        <v>0.2248477393566877</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2921327605383656</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2612549028518297</v>
+      </c>
+      <c r="C95">
+        <v>-12.1198001918023</v>
+      </c>
+      <c r="D95">
+        <v>4.4859998081977</v>
+      </c>
+      <c r="E95">
+        <v>19.5858</v>
+      </c>
+      <c r="F95">
+        <v>21.4458</v>
+      </c>
+      <c r="G95">
+        <v>4.84</v>
+      </c>
+      <c r="H95">
+        <v>21.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.65</v>
+      </c>
+      <c r="K95">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L95">
+        <v>1.48</v>
+      </c>
+      <c r="M95">
+        <v>5.12125704</v>
+      </c>
+      <c r="N95">
+        <v>-3.64125704</v>
+      </c>
+      <c r="O95">
+        <v>-0.7282514079999998</v>
+      </c>
+      <c r="P95">
+        <v>-2.913005632</v>
+      </c>
+      <c r="Q95">
+        <v>-2.743005632</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7429568949096725</v>
+      </c>
+      <c r="T95">
+        <v>10.13347879000419</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05779830961189168</v>
+      </c>
+      <c r="W95">
+        <v>0.2249977636646803</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2889915480594585</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2632549028518297</v>
+      </c>
+      <c r="C96">
+        <v>-12.38976122036102</v>
+      </c>
+      <c r="D96">
+        <v>4.446638779638982</v>
+      </c>
+      <c r="E96">
+        <v>19.8164</v>
+      </c>
+      <c r="F96">
+        <v>21.6764</v>
+      </c>
+      <c r="G96">
+        <v>4.84</v>
+      </c>
+      <c r="H96">
+        <v>21.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.65</v>
+      </c>
+      <c r="K96">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L96">
+        <v>1.48</v>
+      </c>
+      <c r="M96">
+        <v>5.176324320000001</v>
+      </c>
+      <c r="N96">
+        <v>-3.696324320000001</v>
+      </c>
+      <c r="O96">
+        <v>-0.739264864</v>
+      </c>
+      <c r="P96">
+        <v>-2.957059456000001</v>
+      </c>
+      <c r="Q96">
+        <v>-2.787059456000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8603163773946181</v>
+      </c>
+      <c r="T96">
+        <v>11.82239192167156</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05718343397772261</v>
+      </c>
+      <c r="W96">
+        <v>0.2251445959661199</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2859171698886132</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2652549028518297</v>
+      </c>
+      <c r="C97">
+        <v>-12.65903753420854</v>
+      </c>
+      <c r="D97">
+        <v>4.407962465791461</v>
+      </c>
+      <c r="E97">
+        <v>20.047</v>
+      </c>
+      <c r="F97">
+        <v>21.907</v>
+      </c>
+      <c r="G97">
+        <v>4.84</v>
+      </c>
+      <c r="H97">
+        <v>21.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.65</v>
+      </c>
+      <c r="K97">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L97">
+        <v>1.48</v>
+      </c>
+      <c r="M97">
+        <v>5.2313916</v>
+      </c>
+      <c r="N97">
+        <v>-3.7513916</v>
+      </c>
+      <c r="O97">
+        <v>-0.7502783199999998</v>
+      </c>
+      <c r="P97">
+        <v>-3.00111328</v>
+      </c>
+      <c r="Q97">
+        <v>-2.83111328</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.024619652873542</v>
+      </c>
+      <c r="T97">
+        <v>14.18687030600588</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05658150309374659</v>
+      </c>
+      <c r="W97">
+        <v>0.2252883370612133</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2829075154687331</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2672549028518297</v>
+      </c>
+      <c r="C98">
+        <v>-12.92764684597408</v>
+      </c>
+      <c r="D98">
+        <v>4.369953154025914</v>
+      </c>
+      <c r="E98">
+        <v>20.2776</v>
+      </c>
+      <c r="F98">
+        <v>22.1376</v>
+      </c>
+      <c r="G98">
+        <v>4.84</v>
+      </c>
+      <c r="H98">
+        <v>21.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.65</v>
+      </c>
+      <c r="K98">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L98">
+        <v>1.48</v>
+      </c>
+      <c r="M98">
+        <v>5.28645888</v>
+      </c>
+      <c r="N98">
+        <v>-3.80645888</v>
+      </c>
+      <c r="O98">
+        <v>-0.7612917759999998</v>
+      </c>
+      <c r="P98">
+        <v>-3.045167104</v>
+      </c>
+      <c r="Q98">
+        <v>-2.875167104</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.271074566091925</v>
+      </c>
+      <c r="T98">
+        <v>17.73358788250731</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05599211243652007</v>
+      </c>
+      <c r="W98">
+        <v>0.225429083550159</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2799605621826005</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2692549028518297</v>
+      </c>
+      <c r="C99">
+        <v>-13.19560626257467</v>
+      </c>
+      <c r="D99">
+        <v>4.332593737425326</v>
+      </c>
+      <c r="E99">
+        <v>20.5082</v>
+      </c>
+      <c r="F99">
+        <v>22.3682</v>
+      </c>
+      <c r="G99">
+        <v>4.84</v>
+      </c>
+      <c r="H99">
+        <v>21.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.65</v>
+      </c>
+      <c r="K99">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L99">
+        <v>1.48</v>
+      </c>
+      <c r="M99">
+        <v>5.34152616</v>
+      </c>
+      <c r="N99">
+        <v>-3.86152616</v>
+      </c>
+      <c r="O99">
+        <v>-0.7723052319999998</v>
+      </c>
+      <c r="P99">
+        <v>-3.089220928</v>
+      </c>
+      <c r="Q99">
+        <v>-2.919220928</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.681832754789233</v>
+      </c>
+      <c r="T99">
+        <v>23.64478384334307</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05541487416397862</v>
+      </c>
+      <c r="W99">
+        <v>0.2255669280496419</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2770743708198932</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2712549028518297</v>
+      </c>
+      <c r="C100">
+        <v>-13.46293231088727</v>
+      </c>
+      <c r="D100">
+        <v>4.295867689112726</v>
+      </c>
+      <c r="E100">
+        <v>20.7388</v>
+      </c>
+      <c r="F100">
+        <v>22.5988</v>
+      </c>
+      <c r="G100">
+        <v>4.84</v>
+      </c>
+      <c r="H100">
+        <v>21.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.65</v>
+      </c>
+      <c r="K100">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L100">
+        <v>1.48</v>
+      </c>
+      <c r="M100">
+        <v>5.396593439999999</v>
+      </c>
+      <c r="N100">
+        <v>-3.916593439999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.7833186879999997</v>
+      </c>
+      <c r="P100">
+        <v>-3.133274752</v>
+      </c>
+      <c r="Q100">
+        <v>-2.963274752</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.50334913218385</v>
+      </c>
+      <c r="T100">
+        <v>35.46717576501461</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.0548494162643462</v>
+      </c>
+      <c r="W100">
+        <v>0.2257019593960741</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.274247081321731</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2732549028518297</v>
+      </c>
+      <c r="C101">
+        <v>-13.72964096212628</v>
+      </c>
+      <c r="D101">
+        <v>4.259759037873718</v>
+      </c>
+      <c r="E101">
+        <v>20.9694</v>
+      </c>
+      <c r="F101">
+        <v>22.8294</v>
+      </c>
+      <c r="G101">
+        <v>4.84</v>
+      </c>
+      <c r="H101">
+        <v>21.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.65</v>
+      </c>
+      <c r="K101">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="L101">
+        <v>1.48</v>
+      </c>
+      <c r="M101">
+        <v>5.45166072</v>
+      </c>
+      <c r="N101">
+        <v>-3.97166072</v>
+      </c>
+      <c r="O101">
+        <v>-0.794332144</v>
+      </c>
+      <c r="P101">
+        <v>-3.177328576000001</v>
+      </c>
+      <c r="Q101">
+        <v>-3.007328576000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.9678982643677</v>
+      </c>
+      <c r="T101">
+        <v>70.93435153002922</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05429538175662552</v>
+      </c>
+      <c r="W101">
+        <v>0.2258342628365178</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2714769087831276</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
